--- a/research/traditional_assets/database/data/spain/spain_metals_mining.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_metals_mining.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="bme_elz" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,31 +590,31 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.02954128440366972</v>
+        <v>0.04267676767676767</v>
       </c>
       <c r="H2">
-        <v>-0.02954128440366972</v>
+        <v>0.04078643578643579</v>
       </c>
       <c r="I2">
-        <v>-0.3146788990825688</v>
+        <v>-0.02500898651456673</v>
       </c>
       <c r="J2">
-        <v>-0.3146788990825688</v>
+        <v>-0.02500898651456673</v>
       </c>
       <c r="K2">
-        <v>-4.24</v>
+        <v>-5.55</v>
       </c>
       <c r="L2">
-        <v>-0.3889908256880734</v>
+        <v>-0.04004329004329004</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.0006163886874546774</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-0.003063063063063063</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,76 +626,79 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.017</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>0.486</v>
+        <v>2.37</v>
       </c>
       <c r="V2">
-        <v>0.03857142857142857</v>
+        <v>0.08593183466279913</v>
       </c>
       <c r="W2">
-        <v>-0.1796610169491525</v>
+        <v>-0.1067088511574396</v>
       </c>
       <c r="X2">
-        <v>0.1506265950796725</v>
+        <v>0.232543606921889</v>
       </c>
       <c r="Y2">
-        <v>-0.3302876120288251</v>
+        <v>-0.3392524580793286</v>
       </c>
       <c r="Z2">
-        <v>0.4909909909909909</v>
+        <v>1.187302263290225</v>
       </c>
       <c r="AA2">
-        <v>-0.1545045045045045</v>
+        <v>-0.1079586299441578</v>
       </c>
       <c r="AB2">
-        <v>0.1416350200093921</v>
+        <v>0.1116503306982269</v>
       </c>
       <c r="AC2">
-        <v>-0.2961395245138966</v>
+        <v>-0.2196089606423847</v>
       </c>
       <c r="AD2">
-        <v>2.66</v>
+        <v>96.11</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>0.8912276545947418</v>
       </c>
       <c r="AF2">
-        <v>2.66</v>
+        <v>97.00122765459474</v>
       </c>
       <c r="AG2">
-        <v>2.174</v>
+        <v>94.63122765459474</v>
       </c>
       <c r="AH2">
-        <v>0.1743119266055046</v>
+        <v>0.7786183318367483</v>
       </c>
       <c r="AI2">
-        <v>0.128131021194605</v>
+        <v>0.5871701380900535</v>
       </c>
       <c r="AJ2">
-        <v>0.1471503993502098</v>
+        <v>0.7743251538397987</v>
       </c>
       <c r="AK2">
-        <v>0.1072309361744106</v>
+        <v>0.5811614210471406</v>
       </c>
       <c r="AL2">
-        <v>0.246</v>
+        <v>7.386</v>
       </c>
       <c r="AM2">
-        <v>0.105</v>
+        <v>6.815</v>
       </c>
       <c r="AN2">
-        <v>-1.453551912568306</v>
+        <v>162.3479729729729</v>
       </c>
       <c r="AO2">
-        <v>-13.94308943089431</v>
+        <v>-0.4752233956133224</v>
       </c>
       <c r="AP2">
-        <v>-1.187978142076503</v>
+        <v>159.8500467138424</v>
       </c>
       <c r="AQ2">
-        <v>-32.66666666666666</v>
+        <v>-0.5150403521643433</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +709,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Strategic Minerals Europe Corp. (NEOE:SNTA)</t>
+          <t>Asturiana de Laminados, S.A. (BME:ELZ)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,31 +718,31 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.02954128440366972</v>
+        <v>0.05489121676067687</v>
       </c>
       <c r="H3">
-        <v>-0.02954128440366972</v>
+        <v>0.05278001611603546</v>
       </c>
       <c r="I3">
-        <v>-0.3146788990825688</v>
+        <v>0.009296973965197838</v>
       </c>
       <c r="J3">
-        <v>-0.3146788990825688</v>
+        <v>0.009296973965197838</v>
       </c>
       <c r="K3">
-        <v>-4.24</v>
+        <v>-2.88</v>
       </c>
       <c r="L3">
-        <v>-0.3889908256880734</v>
+        <v>-0.02320709105560032</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.017</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.0007083333333333334</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0.005902777777777778</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -749,76 +754,8976 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.017</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>0.486</v>
+        <v>1.32</v>
       </c>
       <c r="V3">
-        <v>0.03857142857142857</v>
+        <v>0.055</v>
       </c>
       <c r="W3">
-        <v>-0.1796610169491525</v>
+        <v>-0.06590389016018305</v>
       </c>
       <c r="X3">
-        <v>0.1506265950796725</v>
+        <v>0.3063635773718648</v>
       </c>
       <c r="Y3">
-        <v>-0.3302876120288251</v>
+        <v>-0.3722674675320479</v>
       </c>
       <c r="Z3">
-        <v>0.4909909909909909</v>
+        <v>1.286527271292599</v>
       </c>
       <c r="AA3">
-        <v>-0.1545045045045045</v>
+        <v>0.01196081054672431</v>
       </c>
       <c r="AB3">
-        <v>0.1416350200093921</v>
+        <v>0.1033682471957174</v>
       </c>
       <c r="AC3">
-        <v>-0.2961395245138966</v>
+        <v>-0.09140743664899309</v>
       </c>
       <c r="AD3">
-        <v>2.66</v>
+        <v>92.5</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>0.8912276545947418</v>
       </c>
       <c r="AF3">
-        <v>2.66</v>
+        <v>93.39122765459474</v>
       </c>
       <c r="AG3">
-        <v>2.174</v>
+        <v>92.07122765459475</v>
       </c>
       <c r="AH3">
-        <v>0.1743119266055046</v>
+        <v>0.7955554219893139</v>
       </c>
       <c r="AI3">
-        <v>0.128131021194605</v>
+        <v>0.6458982966635528</v>
       </c>
       <c r="AJ3">
-        <v>0.1471503993502098</v>
+        <v>0.7932304113176153</v>
       </c>
       <c r="AK3">
-        <v>0.1072309361744106</v>
+        <v>0.6426358534217669</v>
       </c>
       <c r="AL3">
-        <v>0.246</v>
+        <v>6.8</v>
       </c>
       <c r="AM3">
-        <v>0.105</v>
+        <v>6.375</v>
       </c>
       <c r="AN3">
-        <v>-1.453551912568306</v>
+        <v>27.67803710353082</v>
       </c>
       <c r="AO3">
-        <v>-13.94308943089431</v>
+        <v>0.1632352941176471</v>
       </c>
       <c r="AP3">
-        <v>-1.187978142076503</v>
+        <v>27.54973897504331</v>
       </c>
       <c r="AQ3">
-        <v>-32.66666666666666</v>
+        <v>0.1741176470588235</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Strategic Minerals Europe Corp. (NEOE:SNTA)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>-0.06186206896551724</v>
+      </c>
+      <c r="H4">
+        <v>-0.06186206896551724</v>
+      </c>
+      <c r="I4">
+        <v>-0.3186206896551724</v>
+      </c>
+      <c r="J4">
+        <v>-0.3186206896551724</v>
+      </c>
+      <c r="K4">
+        <v>-2.67</v>
+      </c>
+      <c r="L4">
+        <v>-0.1841379310344828</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>1.05</v>
+      </c>
+      <c r="V4">
+        <v>0.2932960893854749</v>
+      </c>
+      <c r="W4">
+        <v>-0.1475138121546961</v>
+      </c>
+      <c r="X4">
+        <v>0.1587236364719133</v>
+      </c>
+      <c r="Y4">
+        <v>-0.3062374486266094</v>
+      </c>
+      <c r="Z4">
+        <v>0.71520173621387</v>
+      </c>
+      <c r="AA4">
+        <v>-0.2278780704350399</v>
+      </c>
+      <c r="AB4">
+        <v>0.1199324142007365</v>
+      </c>
+      <c r="AC4">
+        <v>-0.3478104846357764</v>
+      </c>
+      <c r="AD4">
+        <v>3.61</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>3.61</v>
+      </c>
+      <c r="AG4">
+        <v>2.56</v>
+      </c>
+      <c r="AH4">
+        <v>0.502086230876217</v>
+      </c>
+      <c r="AI4">
+        <v>0.1751576904415332</v>
+      </c>
+      <c r="AJ4">
+        <v>0.4169381107491856</v>
+      </c>
+      <c r="AK4">
+        <v>0.130879345603272</v>
+      </c>
+      <c r="AL4">
+        <v>0.586</v>
+      </c>
+      <c r="AM4">
+        <v>0.4399999999999999</v>
+      </c>
+      <c r="AN4">
+        <v>-1.312727272727273</v>
+      </c>
+      <c r="AO4">
+        <v>-7.883959044368601</v>
+      </c>
+      <c r="AP4">
+        <v>-0.9309090909090908</v>
+      </c>
+      <c r="AQ4">
+        <v>-10.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Asturiana de Laminados, S.A. (BME:ELZ)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BME:ELZ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.163529411764706</v>
+      </c>
+      <c r="F2">
+        <v>4.65882935524924</v>
+      </c>
+      <c r="G2">
+        <v>27.9447120450613</v>
+      </c>
+      <c r="H2">
+        <v>5.62016649453476</v>
+      </c>
+      <c r="I2">
+        <v>0.7955554219893139</v>
+      </c>
+      <c r="J2">
+        <v>0.16</v>
+      </c>
+      <c r="K2">
+        <v>24</v>
+      </c>
+      <c r="L2">
+        <v>97.0426949896807</v>
+      </c>
+      <c r="M2">
+        <v>116.071227654595</v>
+      </c>
+      <c r="N2">
+        <v>114.505291414416</v>
+      </c>
+      <c r="O2">
+        <v>93.3912276545947</v>
+      </c>
+      <c r="P2">
+        <v>18.7825964247352</v>
+      </c>
+      <c r="Q2">
+        <v>0.103368247195717</v>
+      </c>
+      <c r="R2">
+        <v>0.104251261045992</v>
+      </c>
+      <c r="S2">
+        <v>0.051201806657575</v>
+      </c>
+      <c r="T2">
+        <v>0.038175</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.306363577371865</v>
+      </c>
+      <c r="X2">
+        <v>0.116837215530942</v>
+      </c>
+      <c r="Y2">
+        <v>3.85664195952717</v>
+      </c>
+      <c r="Z2">
+        <v>1.12482275344605</v>
+      </c>
+      <c r="AA2">
+        <v>92.5</v>
+      </c>
+      <c r="AB2">
+        <v>0.06826907554343334</v>
+      </c>
+      <c r="AC2">
+        <v>0.1635294117647059</v>
+      </c>
+      <c r="AD2">
+        <v>93.39122765459474</v>
+      </c>
+      <c r="AE2">
+        <v>6.8</v>
+      </c>
+      <c r="AF2">
+        <v>2.23</v>
+      </c>
+      <c r="AG2">
+        <v>3.342</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>24</v>
+      </c>
+      <c r="AK2">
+        <v>0.06937734437880483</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.25</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>1.289999999999999</v>
+      </c>
+      <c r="AR2">
+        <v>6.8</v>
+      </c>
+      <c r="AS2">
+        <v>92.5</v>
+      </c>
+      <c r="AT2">
+        <v>1.32</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1070825635895745</v>
+      </c>
+      <c r="C2">
+        <v>111.0773864472854</v>
+      </c>
+      <c r="D2">
+        <v>109.7573864472854</v>
+      </c>
+      <c r="E2">
+        <v>-93.39122765459474</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1.32</v>
+      </c>
+      <c r="H2">
+        <v>24</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>6.684</v>
+      </c>
+      <c r="K2">
+        <v>2.23</v>
+      </c>
+      <c r="L2">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="O2">
+        <v>1.1135</v>
+      </c>
+      <c r="P2">
+        <v>3.3405</v>
+      </c>
+      <c r="Q2">
+        <v>5.570500000000001</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1070825635895745</v>
+      </c>
+      <c r="T2">
+        <v>0.9842199092652959</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.25</v>
+      </c>
+      <c r="W2">
+        <v>0.033525</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1068591071806005</v>
+      </c>
+      <c r="C3">
+        <v>110.2638372793649</v>
+      </c>
+      <c r="D3">
+        <v>110.1177495559109</v>
+      </c>
+      <c r="E3">
+        <v>-92.2173153780488</v>
+      </c>
+      <c r="F3">
+        <v>1.173912276545948</v>
+      </c>
+      <c r="G3">
+        <v>1.32</v>
+      </c>
+      <c r="H3">
+        <v>24</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>6.684</v>
+      </c>
+      <c r="K3">
+        <v>2.23</v>
+      </c>
+      <c r="L3">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M3">
+        <v>0.05247387876160386</v>
+      </c>
+      <c r="N3">
+        <v>4.401526121238397</v>
+      </c>
+      <c r="O3">
+        <v>1.100381530309599</v>
+      </c>
+      <c r="P3">
+        <v>3.301144590928797</v>
+      </c>
+      <c r="Q3">
+        <v>5.531144590928797</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1075998557379803</v>
+      </c>
+      <c r="T3">
+        <v>0.9916761206991239</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.25</v>
+      </c>
+      <c r="W3">
+        <v>0.033525</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>84.88032722404881</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1066356507716266</v>
+      </c>
+      <c r="C4">
+        <v>109.4526622449646</v>
+      </c>
+      <c r="D4">
+        <v>110.4804867980565</v>
+      </c>
+      <c r="E4">
+        <v>-91.04340310150285</v>
+      </c>
+      <c r="F4">
+        <v>2.347824553091895</v>
+      </c>
+      <c r="G4">
+        <v>1.32</v>
+      </c>
+      <c r="H4">
+        <v>24</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>6.684</v>
+      </c>
+      <c r="K4">
+        <v>2.23</v>
+      </c>
+      <c r="L4">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M4">
+        <v>0.1049477575232077</v>
+      </c>
+      <c r="N4">
+        <v>4.349052242476793</v>
+      </c>
+      <c r="O4">
+        <v>1.087263060619198</v>
+      </c>
+      <c r="P4">
+        <v>3.261789181857595</v>
+      </c>
+      <c r="Q4">
+        <v>5.491789181857595</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1081277048690067</v>
+      </c>
+      <c r="T4">
+        <v>0.9992844997132342</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.25</v>
+      </c>
+      <c r="W4">
+        <v>0.033525</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>42.44016361202441</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1064121943626527</v>
+      </c>
+      <c r="C5">
+        <v>108.6438848834189</v>
+      </c>
+      <c r="D5">
+        <v>110.8456217130567</v>
+      </c>
+      <c r="E5">
+        <v>-89.8694908249569</v>
+      </c>
+      <c r="F5">
+        <v>3.521736829637842</v>
+      </c>
+      <c r="G5">
+        <v>1.32</v>
+      </c>
+      <c r="H5">
+        <v>24</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>6.684</v>
+      </c>
+      <c r="K5">
+        <v>2.23</v>
+      </c>
+      <c r="L5">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M5">
+        <v>0.1574216362848116</v>
+      </c>
+      <c r="N5">
+        <v>4.296578363715189</v>
+      </c>
+      <c r="O5">
+        <v>1.074144590928797</v>
+      </c>
+      <c r="P5">
+        <v>3.222433772786392</v>
+      </c>
+      <c r="Q5">
+        <v>5.452433772786392</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1086664374872708</v>
+      </c>
+      <c r="T5">
+        <v>1.00704975252145</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.25</v>
+      </c>
+      <c r="W5">
+        <v>0.033525</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>28.29344240801627</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1061887379536787</v>
+      </c>
+      <c r="C6">
+        <v>107.8375290462814</v>
+      </c>
+      <c r="D6">
+        <v>111.2131781524652</v>
+      </c>
+      <c r="E6">
+        <v>-88.69557854841095</v>
+      </c>
+      <c r="F6">
+        <v>4.69564910618379</v>
+      </c>
+      <c r="G6">
+        <v>1.32</v>
+      </c>
+      <c r="H6">
+        <v>24</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>6.684</v>
+      </c>
+      <c r="K6">
+        <v>2.23</v>
+      </c>
+      <c r="L6">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M6">
+        <v>0.2098955150464154</v>
+      </c>
+      <c r="N6">
+        <v>4.244104484953585</v>
+      </c>
+      <c r="O6">
+        <v>1.061026121238396</v>
+      </c>
+      <c r="P6">
+        <v>3.183078363715189</v>
+      </c>
+      <c r="Q6">
+        <v>5.413078363715188</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1092163937017487</v>
+      </c>
+      <c r="T6">
+        <v>1.014976781429836</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.25</v>
+      </c>
+      <c r="W6">
+        <v>0.033525</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>21.2200818060122</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1059652815447048</v>
+      </c>
+      <c r="C7">
+        <v>107.0336189025187</v>
+      </c>
+      <c r="D7">
+        <v>111.5831802852484</v>
+      </c>
+      <c r="E7">
+        <v>-87.521666271865</v>
+      </c>
+      <c r="F7">
+        <v>5.869561382729738</v>
+      </c>
+      <c r="G7">
+        <v>1.32</v>
+      </c>
+      <c r="H7">
+        <v>24</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>6.684</v>
+      </c>
+      <c r="K7">
+        <v>2.23</v>
+      </c>
+      <c r="L7">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M7">
+        <v>0.2623693938080193</v>
+      </c>
+      <c r="N7">
+        <v>4.191630606191981</v>
+      </c>
+      <c r="O7">
+        <v>1.047907651547995</v>
+      </c>
+      <c r="P7">
+        <v>3.143722954643986</v>
+      </c>
+      <c r="Q7">
+        <v>5.373722954643986</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1097779279417945</v>
+      </c>
+      <c r="T7">
+        <v>1.023070695157347</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.25</v>
+      </c>
+      <c r="W7">
+        <v>0.033525</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>16.97606544480976</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1057418251357308</v>
+      </c>
+      <c r="C8">
+        <v>106.2321789438081</v>
+      </c>
+      <c r="D8">
+        <v>111.9556526030838</v>
+      </c>
+      <c r="E8">
+        <v>-86.34775399531905</v>
+      </c>
+      <c r="F8">
+        <v>7.043473659275684</v>
+      </c>
+      <c r="G8">
+        <v>1.32</v>
+      </c>
+      <c r="H8">
+        <v>24</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>6.684</v>
+      </c>
+      <c r="K8">
+        <v>2.23</v>
+      </c>
+      <c r="L8">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M8">
+        <v>0.3148432725696231</v>
+      </c>
+      <c r="N8">
+        <v>4.139156727430377</v>
+      </c>
+      <c r="O8">
+        <v>1.034789181857594</v>
+      </c>
+      <c r="P8">
+        <v>3.104367545572783</v>
+      </c>
+      <c r="Q8">
+        <v>5.334367545572783</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1103514097188626</v>
+      </c>
+      <c r="T8">
+        <v>1.03133681981523</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.25</v>
+      </c>
+      <c r="W8">
+        <v>0.033525</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>14.14672120400813</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1055761187267569</v>
+      </c>
+      <c r="C9">
+        <v>105.3360870843652</v>
+      </c>
+      <c r="D9">
+        <v>112.2334730201868</v>
+      </c>
+      <c r="E9">
+        <v>-85.1738417187731</v>
+      </c>
+      <c r="F9">
+        <v>8.217385935821634</v>
+      </c>
+      <c r="G9">
+        <v>1.32</v>
+      </c>
+      <c r="H9">
+        <v>24</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>6.684</v>
+      </c>
+      <c r="K9">
+        <v>2.23</v>
+      </c>
+      <c r="L9">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M9">
+        <v>0.3763562758606308</v>
+      </c>
+      <c r="N9">
+        <v>4.07764372413937</v>
+      </c>
+      <c r="O9">
+        <v>1.019410931034842</v>
+      </c>
+      <c r="P9">
+        <v>3.058232793104527</v>
+      </c>
+      <c r="Q9">
+        <v>5.288232793104527</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.110937224437373</v>
+      </c>
+      <c r="T9">
+        <v>1.039780710594788</v>
+      </c>
+      <c r="U9">
+        <v>0.0458</v>
+      </c>
+      <c r="V9">
+        <v>0.25</v>
+      </c>
+      <c r="W9">
+        <v>0.03435</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>11.83453096355266</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.105360912317783</v>
+      </c>
+      <c r="C10">
+        <v>104.525050884097</v>
+      </c>
+      <c r="D10">
+        <v>112.5963490964646</v>
+      </c>
+      <c r="E10">
+        <v>-83.99992944222717</v>
+      </c>
+      <c r="F10">
+        <v>9.39129821236758</v>
+      </c>
+      <c r="G10">
+        <v>1.32</v>
+      </c>
+      <c r="H10">
+        <v>24</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>6.684</v>
+      </c>
+      <c r="K10">
+        <v>2.23</v>
+      </c>
+      <c r="L10">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M10">
+        <v>0.4301214581264352</v>
+      </c>
+      <c r="N10">
+        <v>4.023878541873565</v>
+      </c>
+      <c r="O10">
+        <v>1.005969635468391</v>
+      </c>
+      <c r="P10">
+        <v>3.017908906405174</v>
+      </c>
+      <c r="Q10">
+        <v>5.247908906405174</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1115357742584598</v>
+      </c>
+      <c r="T10">
+        <v>1.048408164217381</v>
+      </c>
+      <c r="U10">
+        <v>0.0458</v>
+      </c>
+      <c r="V10">
+        <v>0.25</v>
+      </c>
+      <c r="W10">
+        <v>0.03435</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>10.35521459310857</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1052942059088091</v>
+      </c>
+      <c r="C11">
+        <v>103.4640942855556</v>
+      </c>
+      <c r="D11">
+        <v>112.7093047744691</v>
+      </c>
+      <c r="E11">
+        <v>-82.82601716568122</v>
+      </c>
+      <c r="F11">
+        <v>10.56521048891353</v>
+      </c>
+      <c r="G11">
+        <v>1.32</v>
+      </c>
+      <c r="H11">
+        <v>24</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>6.684</v>
+      </c>
+      <c r="K11">
+        <v>2.23</v>
+      </c>
+      <c r="L11">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M11">
+        <v>0.5071301034678493</v>
+      </c>
+      <c r="N11">
+        <v>3.946869896532151</v>
+      </c>
+      <c r="O11">
+        <v>0.9867174741330378</v>
+      </c>
+      <c r="P11">
+        <v>2.960152422399113</v>
+      </c>
+      <c r="Q11">
+        <v>5.190152422399113</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1121474790206693</v>
+      </c>
+      <c r="T11">
+        <v>1.057225232205304</v>
+      </c>
+      <c r="U11">
+        <v>0.048</v>
+      </c>
+      <c r="V11">
+        <v>0.25</v>
+      </c>
+      <c r="W11">
+        <v>0.036</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>8.782756080821718</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1050954994998351</v>
+      </c>
+      <c r="C12">
+        <v>102.6280037522449</v>
+      </c>
+      <c r="D12">
+        <v>113.0471265177043</v>
+      </c>
+      <c r="E12">
+        <v>-81.65210488913527</v>
+      </c>
+      <c r="F12">
+        <v>11.73912276545948</v>
+      </c>
+      <c r="G12">
+        <v>1.32</v>
+      </c>
+      <c r="H12">
+        <v>24</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>6.684</v>
+      </c>
+      <c r="K12">
+        <v>2.23</v>
+      </c>
+      <c r="L12">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M12">
+        <v>0.5634778927420548</v>
+      </c>
+      <c r="N12">
+        <v>3.890522107257946</v>
+      </c>
+      <c r="O12">
+        <v>0.9726305268144865</v>
+      </c>
+      <c r="P12">
+        <v>2.91789158044346</v>
+      </c>
+      <c r="Q12">
+        <v>5.14789158044346</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.112772777222039</v>
+      </c>
+      <c r="T12">
+        <v>1.066238235037404</v>
+      </c>
+      <c r="U12">
+        <v>0.048</v>
+      </c>
+      <c r="V12">
+        <v>0.25</v>
+      </c>
+      <c r="W12">
+        <v>0.036</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>7.904480472739546</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1050205430908612</v>
+      </c>
+      <c r="C13">
+        <v>101.582051867642</v>
+      </c>
+      <c r="D13">
+        <v>113.1750869096474</v>
+      </c>
+      <c r="E13">
+        <v>-80.47819261258932</v>
+      </c>
+      <c r="F13">
+        <v>12.91303504200542</v>
+      </c>
+      <c r="G13">
+        <v>1.32</v>
+      </c>
+      <c r="H13">
+        <v>24</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>6.684</v>
+      </c>
+      <c r="K13">
+        <v>2.23</v>
+      </c>
+      <c r="L13">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M13">
+        <v>0.6391952345792684</v>
+      </c>
+      <c r="N13">
+        <v>3.814804765420732</v>
+      </c>
+      <c r="O13">
+        <v>0.9537011913551831</v>
+      </c>
+      <c r="P13">
+        <v>2.861103574065549</v>
+      </c>
+      <c r="Q13">
+        <v>5.091103574065549</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1134121270683834</v>
+      </c>
+      <c r="T13">
+        <v>1.075453777258989</v>
+      </c>
+      <c r="U13">
+        <v>0.0495</v>
+      </c>
+      <c r="V13">
+        <v>0.25</v>
+      </c>
+      <c r="W13">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>6.968137055858553</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1048330866818872</v>
+      </c>
+      <c r="C14">
+        <v>100.7294239114792</v>
+      </c>
+      <c r="D14">
+        <v>113.4963712300306</v>
+      </c>
+      <c r="E14">
+        <v>-79.30428033604338</v>
+      </c>
+      <c r="F14">
+        <v>14.08694731855137</v>
+      </c>
+      <c r="G14">
+        <v>1.32</v>
+      </c>
+      <c r="H14">
+        <v>24</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>6.684</v>
+      </c>
+      <c r="K14">
+        <v>2.23</v>
+      </c>
+      <c r="L14">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M14">
+        <v>0.6973038922682928</v>
+      </c>
+      <c r="N14">
+        <v>3.756696107731708</v>
+      </c>
+      <c r="O14">
+        <v>0.939174026932927</v>
+      </c>
+      <c r="P14">
+        <v>2.817522080798781</v>
+      </c>
+      <c r="Q14">
+        <v>5.047522080798781</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1140660075930537</v>
+      </c>
+      <c r="T14">
+        <v>1.084878763621974</v>
+      </c>
+      <c r="U14">
+        <v>0.0495</v>
+      </c>
+      <c r="V14">
+        <v>0.25</v>
+      </c>
+      <c r="W14">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>6.38745896787034</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1047821302729133</v>
+      </c>
+      <c r="C15">
+        <v>99.64316214705731</v>
+      </c>
+      <c r="D15">
+        <v>113.5840217421546</v>
+      </c>
+      <c r="E15">
+        <v>-78.13036805949743</v>
+      </c>
+      <c r="F15">
+        <v>15.26085959509732</v>
+      </c>
+      <c r="G15">
+        <v>1.32</v>
+      </c>
+      <c r="H15">
+        <v>24</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>6.684</v>
+      </c>
+      <c r="K15">
+        <v>2.23</v>
+      </c>
+      <c r="L15">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M15">
+        <v>0.7767777533904534</v>
+      </c>
+      <c r="N15">
+        <v>3.677222246609547</v>
+      </c>
+      <c r="O15">
+        <v>0.9193055616523869</v>
+      </c>
+      <c r="P15">
+        <v>2.757916684957161</v>
+      </c>
+      <c r="Q15">
+        <v>4.987916684957161</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1147349198539233</v>
+      </c>
+      <c r="T15">
+        <v>1.094520416338131</v>
+      </c>
+      <c r="U15">
+        <v>0.0509</v>
+      </c>
+      <c r="V15">
+        <v>0.25</v>
+      </c>
+      <c r="W15">
+        <v>0.038175</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>5.733943821845221</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1046051738639394</v>
+      </c>
+      <c r="C16">
+        <v>98.77468817306594</v>
+      </c>
+      <c r="D16">
+        <v>113.8894600447092</v>
+      </c>
+      <c r="E16">
+        <v>-76.95645578295148</v>
+      </c>
+      <c r="F16">
+        <v>16.43477187164327</v>
+      </c>
+      <c r="G16">
+        <v>1.32</v>
+      </c>
+      <c r="H16">
+        <v>24</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>6.684</v>
+      </c>
+      <c r="K16">
+        <v>2.23</v>
+      </c>
+      <c r="L16">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M16">
+        <v>0.8365298882666423</v>
+      </c>
+      <c r="N16">
+        <v>3.617470111733359</v>
+      </c>
+      <c r="O16">
+        <v>0.9043675279333396</v>
+      </c>
+      <c r="P16">
+        <v>2.713102583800019</v>
+      </c>
+      <c r="Q16">
+        <v>4.94310258380002</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.115419388213883</v>
+      </c>
+      <c r="T16">
+        <v>1.104386293536059</v>
+      </c>
+      <c r="U16">
+        <v>0.0509</v>
+      </c>
+      <c r="V16">
+        <v>0.25</v>
+      </c>
+      <c r="W16">
+        <v>0.038175</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>5.324376405999132</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1044282174549654</v>
+      </c>
+      <c r="C17">
+        <v>97.90786133401983</v>
+      </c>
+      <c r="D17">
+        <v>114.196545482209</v>
+      </c>
+      <c r="E17">
+        <v>-75.78254350640553</v>
+      </c>
+      <c r="F17">
+        <v>17.60868414818921</v>
+      </c>
+      <c r="G17">
+        <v>1.32</v>
+      </c>
+      <c r="H17">
+        <v>24</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>6.684</v>
+      </c>
+      <c r="K17">
+        <v>2.23</v>
+      </c>
+      <c r="L17">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M17">
+        <v>0.8962820231428309</v>
+      </c>
+      <c r="N17">
+        <v>3.55771797685717</v>
+      </c>
+      <c r="O17">
+        <v>0.8894294942142924</v>
+      </c>
+      <c r="P17">
+        <v>2.668288482642877</v>
+      </c>
+      <c r="Q17">
+        <v>4.898288482642878</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.116119961711724</v>
+      </c>
+      <c r="T17">
+        <v>1.114484309020997</v>
+      </c>
+      <c r="U17">
+        <v>0.0509</v>
+      </c>
+      <c r="V17">
+        <v>0.25</v>
+      </c>
+      <c r="W17">
+        <v>0.038175</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>4.969417978932524</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1042512610459915</v>
+      </c>
+      <c r="C18">
+        <v>97.04269498968073</v>
+      </c>
+      <c r="D18">
+        <v>114.5052914144159</v>
+      </c>
+      <c r="E18">
+        <v>-74.60863122985958</v>
+      </c>
+      <c r="F18">
+        <v>18.78259642473516</v>
+      </c>
+      <c r="G18">
+        <v>1.32</v>
+      </c>
+      <c r="H18">
+        <v>24</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>6.684</v>
+      </c>
+      <c r="K18">
+        <v>2.23</v>
+      </c>
+      <c r="L18">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M18">
+        <v>0.9560341580190197</v>
+      </c>
+      <c r="N18">
+        <v>3.497965841980981</v>
+      </c>
+      <c r="O18">
+        <v>0.8744914604952452</v>
+      </c>
+      <c r="P18">
+        <v>2.623474381485735</v>
+      </c>
+      <c r="Q18">
+        <v>4.853474381485736</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1168372155309423</v>
+      </c>
+      <c r="T18">
+        <v>1.124822753446052</v>
+      </c>
+      <c r="U18">
+        <v>0.0509</v>
+      </c>
+      <c r="V18">
+        <v>0.25</v>
+      </c>
+      <c r="W18">
+        <v>0.038175</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>4.658829355249241</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1044058046370176</v>
+      </c>
+      <c r="C19">
+        <v>95.59904958472369</v>
+      </c>
+      <c r="D19">
+        <v>114.2355582860048</v>
+      </c>
+      <c r="E19">
+        <v>-73.43471895331363</v>
+      </c>
+      <c r="F19">
+        <v>19.95650870128111</v>
+      </c>
+      <c r="G19">
+        <v>1.32</v>
+      </c>
+      <c r="H19">
+        <v>24</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>6.684</v>
+      </c>
+      <c r="K19">
+        <v>2.23</v>
+      </c>
+      <c r="L19">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M19">
+        <v>1.067673215518539</v>
+      </c>
+      <c r="N19">
+        <v>3.386326784481462</v>
+      </c>
+      <c r="O19">
+        <v>0.8465816961203654</v>
+      </c>
+      <c r="P19">
+        <v>2.539745088361096</v>
+      </c>
+      <c r="Q19">
+        <v>4.769745088361097</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.11757175257472</v>
+      </c>
+      <c r="T19">
+        <v>1.135410317013881</v>
+      </c>
+      <c r="U19">
+        <v>0.0535</v>
+      </c>
+      <c r="V19">
+        <v>0.25</v>
+      </c>
+      <c r="W19">
+        <v>0.040125</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>4.171688429813065</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1046128482280436</v>
+      </c>
+      <c r="C20">
+        <v>94.0657585417635</v>
+      </c>
+      <c r="D20">
+        <v>113.8761795195906</v>
+      </c>
+      <c r="E20">
+        <v>-72.26080667676769</v>
+      </c>
+      <c r="F20">
+        <v>21.13042097782705</v>
+      </c>
+      <c r="G20">
+        <v>1.32</v>
+      </c>
+      <c r="H20">
+        <v>24</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>6.684</v>
+      </c>
+      <c r="K20">
+        <v>2.23</v>
+      </c>
+      <c r="L20">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M20">
+        <v>1.18752965895388</v>
+      </c>
+      <c r="N20">
+        <v>3.26647034104612</v>
+      </c>
+      <c r="O20">
+        <v>0.8166175852615301</v>
+      </c>
+      <c r="P20">
+        <v>2.44985275578459</v>
+      </c>
+      <c r="Q20">
+        <v>4.679852755784591</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1183242051561508</v>
+      </c>
+      <c r="T20">
+        <v>1.14625611383946</v>
+      </c>
+      <c r="U20">
+        <v>0.0562</v>
+      </c>
+      <c r="V20">
+        <v>0.25</v>
+      </c>
+      <c r="W20">
+        <v>0.04215</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>3.750643166187211</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1044756418190697</v>
+      </c>
+      <c r="C21">
+        <v>93.12975093164772</v>
+      </c>
+      <c r="D21">
+        <v>114.1140841860207</v>
+      </c>
+      <c r="E21">
+        <v>-71.08689440022174</v>
+      </c>
+      <c r="F21">
+        <v>22.304333254373</v>
+      </c>
+      <c r="G21">
+        <v>1.32</v>
+      </c>
+      <c r="H21">
+        <v>24</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>6.684</v>
+      </c>
+      <c r="K21">
+        <v>2.23</v>
+      </c>
+      <c r="L21">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M21">
+        <v>1.253503528895763</v>
+      </c>
+      <c r="N21">
+        <v>3.200496471104238</v>
+      </c>
+      <c r="O21">
+        <v>0.8001241177760594</v>
+      </c>
+      <c r="P21">
+        <v>2.400372353328178</v>
+      </c>
+      <c r="Q21">
+        <v>4.630372353328179</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1190952368136663</v>
+      </c>
+      <c r="T21">
+        <v>1.157369708117524</v>
+      </c>
+      <c r="U21">
+        <v>0.0562</v>
+      </c>
+      <c r="V21">
+        <v>0.25</v>
+      </c>
+      <c r="W21">
+        <v>0.04215</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>3.55324089428262</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1050434354100958</v>
+      </c>
+      <c r="C22">
+        <v>90.97773048112934</v>
+      </c>
+      <c r="D22">
+        <v>113.1359760120483</v>
+      </c>
+      <c r="E22">
+        <v>-69.91298212367579</v>
+      </c>
+      <c r="F22">
+        <v>23.47824553091895</v>
+      </c>
+      <c r="G22">
+        <v>1.32</v>
+      </c>
+      <c r="H22">
+        <v>24</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>6.684</v>
+      </c>
+      <c r="K22">
+        <v>2.23</v>
+      </c>
+      <c r="L22">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M22">
+        <v>1.429825152832964</v>
+      </c>
+      <c r="N22">
+        <v>3.024174847167036</v>
+      </c>
+      <c r="O22">
+        <v>0.7560437117917591</v>
+      </c>
+      <c r="P22">
+        <v>2.268131135375278</v>
+      </c>
+      <c r="Q22">
+        <v>4.498131135375278</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1198855442626197</v>
+      </c>
+      <c r="T22">
+        <v>1.168761142252539</v>
+      </c>
+      <c r="U22">
+        <v>0.0609</v>
+      </c>
+      <c r="V22">
+        <v>0.25</v>
+      </c>
+      <c r="W22">
+        <v>0.045675</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>3.115066196153515</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1064062290011218</v>
+      </c>
+      <c r="C23">
+        <v>87.5232445754709</v>
+      </c>
+      <c r="D23">
+        <v>110.8554023829358</v>
+      </c>
+      <c r="E23">
+        <v>-68.73906984712985</v>
+      </c>
+      <c r="F23">
+        <v>24.6521578074649</v>
+      </c>
+      <c r="G23">
+        <v>1.32</v>
+      </c>
+      <c r="H23">
+        <v>24</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>6.684</v>
+      </c>
+      <c r="K23">
+        <v>2.23</v>
+      </c>
+      <c r="L23">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M23">
+        <v>1.730581478084036</v>
+      </c>
+      <c r="N23">
+        <v>2.723418521915965</v>
+      </c>
+      <c r="O23">
+        <v>0.6808546304789913</v>
+      </c>
+      <c r="P23">
+        <v>2.042563891436974</v>
+      </c>
+      <c r="Q23">
+        <v>4.272563891436974</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1206958594950909</v>
+      </c>
+      <c r="T23">
+        <v>1.180440967125149</v>
+      </c>
+      <c r="U23">
+        <v>0.0702</v>
+      </c>
+      <c r="V23">
+        <v>0.25</v>
+      </c>
+      <c r="W23">
+        <v>0.05265</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>2.573701415625412</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1071495225921479</v>
+      </c>
+      <c r="C24">
+        <v>85.14379190892791</v>
+      </c>
+      <c r="D24">
+        <v>109.6498619929388</v>
+      </c>
+      <c r="E24">
+        <v>-67.56515757058389</v>
+      </c>
+      <c r="F24">
+        <v>25.82607008401084</v>
+      </c>
+      <c r="G24">
+        <v>1.32</v>
+      </c>
+      <c r="H24">
+        <v>24</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>6.684</v>
+      </c>
+      <c r="K24">
+        <v>2.23</v>
+      </c>
+      <c r="L24">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M24">
+        <v>1.934372649292412</v>
+      </c>
+      <c r="N24">
+        <v>2.519627350707589</v>
+      </c>
+      <c r="O24">
+        <v>0.6299068376768971</v>
+      </c>
+      <c r="P24">
+        <v>1.889720513030691</v>
+      </c>
+      <c r="Q24">
+        <v>4.119720513030691</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1215269520412152</v>
+      </c>
+      <c r="T24">
+        <v>1.192420274686801</v>
+      </c>
+      <c r="U24">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V24">
+        <v>0.25</v>
+      </c>
+      <c r="W24">
+        <v>0.056175</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>2.302555302169549</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1071525661831739</v>
+      </c>
+      <c r="C25">
+        <v>83.96499716264302</v>
+      </c>
+      <c r="D25">
+        <v>109.6449795231998</v>
+      </c>
+      <c r="E25">
+        <v>-66.39124529403796</v>
+      </c>
+      <c r="F25">
+        <v>26.99998236055679</v>
+      </c>
+      <c r="G25">
+        <v>1.32</v>
+      </c>
+      <c r="H25">
+        <v>24</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>6.684</v>
+      </c>
+      <c r="K25">
+        <v>2.23</v>
+      </c>
+      <c r="L25">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M25">
+        <v>2.022298678805704</v>
+      </c>
+      <c r="N25">
+        <v>2.431701321194297</v>
+      </c>
+      <c r="O25">
+        <v>0.6079253302985742</v>
+      </c>
+      <c r="P25">
+        <v>1.823775990895723</v>
+      </c>
+      <c r="Q25">
+        <v>4.053775990895723</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1223796314067194</v>
+      </c>
+      <c r="T25">
+        <v>1.20471073309421</v>
+      </c>
+      <c r="U25">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V25">
+        <v>0.25</v>
+      </c>
+      <c r="W25">
+        <v>0.056175</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>2.20244420207522</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1071556097742</v>
+      </c>
+      <c r="C26">
+        <v>82.78620285115021</v>
+      </c>
+      <c r="D26">
+        <v>109.6400974882529</v>
+      </c>
+      <c r="E26">
+        <v>-65.21733301749201</v>
+      </c>
+      <c r="F26">
+        <v>28.17389463710274</v>
+      </c>
+      <c r="G26">
+        <v>1.32</v>
+      </c>
+      <c r="H26">
+        <v>24</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>6.684</v>
+      </c>
+      <c r="K26">
+        <v>2.23</v>
+      </c>
+      <c r="L26">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M26">
+        <v>2.110224708318995</v>
+      </c>
+      <c r="N26">
+        <v>2.343775291681006</v>
+      </c>
+      <c r="O26">
+        <v>0.5859438229202515</v>
+      </c>
+      <c r="P26">
+        <v>1.757831468760755</v>
+      </c>
+      <c r="Q26">
+        <v>3.987831468760755</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1232547497028948</v>
+      </c>
+      <c r="T26">
+        <v>1.217324624617603</v>
+      </c>
+      <c r="U26">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V26">
+        <v>0.25</v>
+      </c>
+      <c r="W26">
+        <v>0.056175</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>2.11067569365542</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1071586533652261</v>
+      </c>
+      <c r="C27">
+        <v>81.60740897439152</v>
+      </c>
+      <c r="D27">
+        <v>109.6352158880402</v>
+      </c>
+      <c r="E27">
+        <v>-64.04342074094606</v>
+      </c>
+      <c r="F27">
+        <v>29.34780691364869</v>
+      </c>
+      <c r="G27">
+        <v>1.32</v>
+      </c>
+      <c r="H27">
+        <v>24</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>6.684</v>
+      </c>
+      <c r="K27">
+        <v>2.23</v>
+      </c>
+      <c r="L27">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M27">
+        <v>2.198150737832286</v>
+      </c>
+      <c r="N27">
+        <v>2.255849262167714</v>
+      </c>
+      <c r="O27">
+        <v>0.5639623155419285</v>
+      </c>
+      <c r="P27">
+        <v>1.691886946625786</v>
+      </c>
+      <c r="Q27">
+        <v>3.921886946625786</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1241532044869681</v>
+      </c>
+      <c r="T27">
+        <v>1.23027488658162</v>
+      </c>
+      <c r="U27">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V27">
+        <v>0.25</v>
+      </c>
+      <c r="W27">
+        <v>0.056175</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>2.026248665909203</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1103401969562521</v>
+      </c>
+      <c r="C28">
+        <v>75.55778719046671</v>
+      </c>
+      <c r="D28">
+        <v>104.7595063806613</v>
+      </c>
+      <c r="E28">
+        <v>-62.86950846440011</v>
+      </c>
+      <c r="F28">
+        <v>30.52171919019463</v>
+      </c>
+      <c r="G28">
+        <v>1.32</v>
+      </c>
+      <c r="H28">
+        <v>24</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>6.684</v>
+      </c>
+      <c r="K28">
+        <v>2.23</v>
+      </c>
+      <c r="L28">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M28">
+        <v>2.783580790145751</v>
+      </c>
+      <c r="N28">
+        <v>1.67041920985425</v>
+      </c>
+      <c r="O28">
+        <v>0.4176048024635625</v>
+      </c>
+      <c r="P28">
+        <v>1.252814407390687</v>
+      </c>
+      <c r="Q28">
+        <v>3.482814407390687</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1250759418327732</v>
+      </c>
+      <c r="T28">
+        <v>1.243575155625745</v>
+      </c>
+      <c r="U28">
+        <v>0.0912</v>
+      </c>
+      <c r="V28">
+        <v>0.25</v>
+      </c>
+      <c r="W28">
+        <v>0.0684</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>1.600097261688167</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1104654905472782</v>
+      </c>
+      <c r="C29">
+        <v>74.20072267916571</v>
+      </c>
+      <c r="D29">
+        <v>104.5763541459063</v>
+      </c>
+      <c r="E29">
+        <v>-61.69559618785416</v>
+      </c>
+      <c r="F29">
+        <v>31.69563146674058</v>
+      </c>
+      <c r="G29">
+        <v>1.32</v>
+      </c>
+      <c r="H29">
+        <v>24</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>6.684</v>
+      </c>
+      <c r="K29">
+        <v>2.23</v>
+      </c>
+      <c r="L29">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M29">
+        <v>2.890641589766741</v>
+      </c>
+      <c r="N29">
+        <v>1.563358410233259</v>
+      </c>
+      <c r="O29">
+        <v>0.3908396025583148</v>
+      </c>
+      <c r="P29">
+        <v>1.172518807674944</v>
+      </c>
+      <c r="Q29">
+        <v>3.402518807674944</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1260239596538058</v>
+      </c>
+      <c r="T29">
+        <v>1.257239815602587</v>
+      </c>
+      <c r="U29">
+        <v>0.0912</v>
+      </c>
+      <c r="V29">
+        <v>0.25</v>
+      </c>
+      <c r="W29">
+        <v>0.0684</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>1.540834400144161</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1264452621906978</v>
+      </c>
+      <c r="C30">
+        <v>53.96010654683135</v>
+      </c>
+      <c r="D30">
+        <v>85.50965029011789</v>
+      </c>
+      <c r="E30">
+        <v>-60.52168391130821</v>
+      </c>
+      <c r="F30">
+        <v>32.86954374328653</v>
+      </c>
+      <c r="G30">
+        <v>1.32</v>
+      </c>
+      <c r="H30">
+        <v>24</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>6.684</v>
+      </c>
+      <c r="K30">
+        <v>2.23</v>
+      </c>
+      <c r="L30">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M30">
+        <v>5.147370550198672</v>
+      </c>
+      <c r="N30">
+        <v>-0.6933705501986713</v>
+      </c>
+      <c r="O30">
+        <v>-0.1733426375496678</v>
+      </c>
+      <c r="P30">
+        <v>-0.5200279126490035</v>
+      </c>
+      <c r="Q30">
+        <v>1.709972087350996</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1278925538305352</v>
+      </c>
+      <c r="T30">
+        <v>1.28417359626918</v>
+      </c>
+      <c r="U30">
+        <v>0.1566</v>
+      </c>
+      <c r="V30">
+        <v>0.2163240413995496</v>
+      </c>
+      <c r="W30">
+        <v>0.1227236551168305</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.8652961655981986</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1276232621906978</v>
+      </c>
+      <c r="C31">
+        <v>51.65214035740958</v>
+      </c>
+      <c r="D31">
+        <v>84.37559637724206</v>
+      </c>
+      <c r="E31">
+        <v>-59.34777163476227</v>
+      </c>
+      <c r="F31">
+        <v>34.04345601983248</v>
+      </c>
+      <c r="G31">
+        <v>1.32</v>
+      </c>
+      <c r="H31">
+        <v>24</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>6.684</v>
+      </c>
+      <c r="K31">
+        <v>2.23</v>
+      </c>
+      <c r="L31">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M31">
+        <v>5.331205212705767</v>
+      </c>
+      <c r="N31">
+        <v>-0.8772052127057659</v>
+      </c>
+      <c r="O31">
+        <v>-0.2193013031764415</v>
+      </c>
+      <c r="P31">
+        <v>-0.6579039095293244</v>
+      </c>
+      <c r="Q31">
+        <v>1.572096090470676</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1291473785323737</v>
+      </c>
+      <c r="T31">
+        <v>1.302260548329309</v>
+      </c>
+      <c r="U31">
+        <v>0.1566</v>
+      </c>
+      <c r="V31">
+        <v>0.2088645916961169</v>
+      </c>
+      <c r="W31">
+        <v>0.1238918049403881</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.8354583667844677</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1288012621906978</v>
+      </c>
+      <c r="C32">
+        <v>49.37386076297213</v>
+      </c>
+      <c r="D32">
+        <v>83.27122905935056</v>
+      </c>
+      <c r="E32">
+        <v>-58.17385935821632</v>
+      </c>
+      <c r="F32">
+        <v>35.21736829637842</v>
+      </c>
+      <c r="G32">
+        <v>1.32</v>
+      </c>
+      <c r="H32">
+        <v>24</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>6.684</v>
+      </c>
+      <c r="K32">
+        <v>2.23</v>
+      </c>
+      <c r="L32">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M32">
+        <v>5.515039875212862</v>
+      </c>
+      <c r="N32">
+        <v>-1.061039875212861</v>
+      </c>
+      <c r="O32">
+        <v>-0.2652599688032153</v>
+      </c>
+      <c r="P32">
+        <v>-0.795779906409646</v>
+      </c>
+      <c r="Q32">
+        <v>1.434220093590354</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1304380553685504</v>
+      </c>
+      <c r="T32">
+        <v>1.320864270448299</v>
+      </c>
+      <c r="U32">
+        <v>0.1566</v>
+      </c>
+      <c r="V32">
+        <v>0.2019024386395797</v>
+      </c>
+      <c r="W32">
+        <v>0.1249820781090418</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.8076097545583187</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1471952433985951</v>
+      </c>
+      <c r="C33">
+        <v>34.06935221253046</v>
+      </c>
+      <c r="D33">
+        <v>69.14063278545484</v>
+      </c>
+      <c r="E33">
+        <v>-56.99994708167037</v>
+      </c>
+      <c r="F33">
+        <v>36.39128057292437</v>
+      </c>
+      <c r="G33">
+        <v>1.32</v>
+      </c>
+      <c r="H33">
+        <v>24</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>6.684</v>
+      </c>
+      <c r="K33">
+        <v>2.23</v>
+      </c>
+      <c r="L33">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M33">
+        <v>7.59849938362661</v>
+      </c>
+      <c r="N33">
+        <v>-3.144499383626609</v>
+      </c>
+      <c r="O33">
+        <v>-0.7861248459066523</v>
+      </c>
+      <c r="P33">
+        <v>-2.358374537719957</v>
+      </c>
+      <c r="Q33">
+        <v>-0.128374537719957</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1332646666172211</v>
+      </c>
+      <c r="T33">
+        <v>1.361606839567653</v>
+      </c>
+      <c r="U33">
+        <v>0.2088</v>
+      </c>
+      <c r="V33">
+        <v>0.1465420925609853</v>
+      </c>
+      <c r="W33">
+        <v>0.1782020110732663</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.5861683702439411</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1488952433985951</v>
+      </c>
+      <c r="C34">
+        <v>31.82782727528375</v>
+      </c>
+      <c r="D34">
+        <v>68.07302012475408</v>
+      </c>
+      <c r="E34">
+        <v>-55.82603480512442</v>
+      </c>
+      <c r="F34">
+        <v>37.56519284947032</v>
+      </c>
+      <c r="G34">
+        <v>1.32</v>
+      </c>
+      <c r="H34">
+        <v>24</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>6.684</v>
+      </c>
+      <c r="K34">
+        <v>2.23</v>
+      </c>
+      <c r="L34">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M34">
+        <v>7.843612266969403</v>
+      </c>
+      <c r="N34">
+        <v>-3.389612266969403</v>
+      </c>
+      <c r="O34">
+        <v>-0.8474030667423507</v>
+      </c>
+      <c r="P34">
+        <v>-2.542209200227052</v>
+      </c>
+      <c r="Q34">
+        <v>-0.312209200227052</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1346538528910038</v>
+      </c>
+      <c r="T34">
+        <v>1.381630469561295</v>
+      </c>
+      <c r="U34">
+        <v>0.2088</v>
+      </c>
+      <c r="V34">
+        <v>0.1419626521684545</v>
+      </c>
+      <c r="W34">
+        <v>0.1791581982272267</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.567850608673818</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1505952433985951</v>
+      </c>
+      <c r="C35">
+        <v>29.61877136745217</v>
+      </c>
+      <c r="D35">
+        <v>67.03787649346845</v>
+      </c>
+      <c r="E35">
+        <v>-54.65212252857847</v>
+      </c>
+      <c r="F35">
+        <v>38.73910512601627</v>
+      </c>
+      <c r="G35">
+        <v>1.32</v>
+      </c>
+      <c r="H35">
+        <v>24</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>6.684</v>
+      </c>
+      <c r="K35">
+        <v>2.23</v>
+      </c>
+      <c r="L35">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M35">
+        <v>8.088725150312198</v>
+      </c>
+      <c r="N35">
+        <v>-3.634725150312198</v>
+      </c>
+      <c r="O35">
+        <v>-0.9086812875780494</v>
+      </c>
+      <c r="P35">
+        <v>-2.726043862734148</v>
+      </c>
+      <c r="Q35">
+        <v>-0.4960438627341484</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1360845074117651</v>
+      </c>
+      <c r="T35">
+        <v>1.402251819853255</v>
+      </c>
+      <c r="U35">
+        <v>0.2088</v>
+      </c>
+      <c r="V35">
+        <v>0.1376607536178952</v>
+      </c>
+      <c r="W35">
+        <v>0.1800564346445835</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.5506430144715809</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1522952433985951</v>
+      </c>
+      <c r="C36">
+        <v>27.44072546709741</v>
+      </c>
+      <c r="D36">
+        <v>66.03374286965963</v>
+      </c>
+      <c r="E36">
+        <v>-53.47821025203253</v>
+      </c>
+      <c r="F36">
+        <v>39.91301740256222</v>
+      </c>
+      <c r="G36">
+        <v>1.32</v>
+      </c>
+      <c r="H36">
+        <v>24</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>6.684</v>
+      </c>
+      <c r="K36">
+        <v>2.23</v>
+      </c>
+      <c r="L36">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M36">
+        <v>8.333838033654992</v>
+      </c>
+      <c r="N36">
+        <v>-3.879838033654991</v>
+      </c>
+      <c r="O36">
+        <v>-0.9699595084137478</v>
+      </c>
+      <c r="P36">
+        <v>-2.909878525241243</v>
+      </c>
+      <c r="Q36">
+        <v>-0.6798785252412434</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1375585150998221</v>
+      </c>
+      <c r="T36">
+        <v>1.423498059548001</v>
+      </c>
+      <c r="U36">
+        <v>0.2088</v>
+      </c>
+      <c r="V36">
+        <v>0.1336119079232513</v>
+      </c>
+      <c r="W36">
+        <v>0.1809018336256251</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.5344476316930051</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1539952433985951</v>
+      </c>
+      <c r="C37">
+        <v>25.29231667865999</v>
+      </c>
+      <c r="D37">
+        <v>65.05924635776816</v>
+      </c>
+      <c r="E37">
+        <v>-52.30429797548658</v>
+      </c>
+      <c r="F37">
+        <v>41.08692967910817</v>
+      </c>
+      <c r="G37">
+        <v>1.32</v>
+      </c>
+      <c r="H37">
+        <v>24</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>6.684</v>
+      </c>
+      <c r="K37">
+        <v>2.23</v>
+      </c>
+      <c r="L37">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M37">
+        <v>8.578950916997785</v>
+      </c>
+      <c r="N37">
+        <v>-4.124950916997784</v>
+      </c>
+      <c r="O37">
+        <v>-1.031237729249446</v>
+      </c>
+      <c r="P37">
+        <v>-3.093713187748338</v>
+      </c>
+      <c r="Q37">
+        <v>-0.8637131877483384</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1390778768705886</v>
+      </c>
+      <c r="T37">
+        <v>1.445398029694894</v>
+      </c>
+      <c r="U37">
+        <v>0.2088</v>
+      </c>
+      <c r="V37">
+        <v>0.1297944248397298</v>
+      </c>
+      <c r="W37">
+        <v>0.1816989240934644</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.5191776993589192</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1556952433985951</v>
+      </c>
+      <c r="C38">
+        <v>23.17225197030742</v>
+      </c>
+      <c r="D38">
+        <v>64.11309392596154</v>
+      </c>
+      <c r="E38">
+        <v>-51.13038569894064</v>
+      </c>
+      <c r="F38">
+        <v>42.26084195565411</v>
+      </c>
+      <c r="G38">
+        <v>1.32</v>
+      </c>
+      <c r="H38">
+        <v>24</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>6.684</v>
+      </c>
+      <c r="K38">
+        <v>2.23</v>
+      </c>
+      <c r="L38">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M38">
+        <v>8.824063800340578</v>
+      </c>
+      <c r="N38">
+        <v>-4.370063800340578</v>
+      </c>
+      <c r="O38">
+        <v>-1.092515950085144</v>
+      </c>
+      <c r="P38">
+        <v>-3.277547850255433</v>
+      </c>
+      <c r="Q38">
+        <v>-1.047547850255433</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1406447186966915</v>
+      </c>
+      <c r="T38">
+        <v>1.467982373908876</v>
+      </c>
+      <c r="U38">
+        <v>0.2088</v>
+      </c>
+      <c r="V38">
+        <v>0.1261890241497373</v>
+      </c>
+      <c r="W38">
+        <v>0.1824517317575348</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.5047560965989493</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1688849348086067</v>
+      </c>
+      <c r="C39">
+        <v>15.49772587965079</v>
+      </c>
+      <c r="D39">
+        <v>57.61248011185084</v>
+      </c>
+      <c r="E39">
+        <v>-49.95647342239469</v>
+      </c>
+      <c r="F39">
+        <v>43.43475423220006</v>
+      </c>
+      <c r="G39">
+        <v>1.32</v>
+      </c>
+      <c r="H39">
+        <v>24</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>6.684</v>
+      </c>
+      <c r="K39">
+        <v>2.23</v>
+      </c>
+      <c r="L39">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M39">
+        <v>10.37221931064937</v>
+      </c>
+      <c r="N39">
+        <v>-5.918219310649373</v>
+      </c>
+      <c r="O39">
+        <v>-1.479554827662343</v>
+      </c>
+      <c r="P39">
+        <v>-4.43866448298703</v>
+      </c>
+      <c r="Q39">
+        <v>-2.20866448298703</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1428798593268161</v>
+      </c>
+      <c r="T39">
+        <v>1.50019952851659</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.1073540740559493</v>
+      </c>
+      <c r="W39">
+        <v>0.2131638471154393</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.4294162962237972</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1708849348086067</v>
+      </c>
+      <c r="C40">
+        <v>13.45145855072384</v>
+      </c>
+      <c r="D40">
+        <v>56.74012505946985</v>
+      </c>
+      <c r="E40">
+        <v>-48.78256114584874</v>
+      </c>
+      <c r="F40">
+        <v>44.608666508746</v>
+      </c>
+      <c r="G40">
+        <v>1.32</v>
+      </c>
+      <c r="H40">
+        <v>24</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>6.684</v>
+      </c>
+      <c r="K40">
+        <v>2.23</v>
+      </c>
+      <c r="L40">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M40">
+        <v>10.65254956228855</v>
+      </c>
+      <c r="N40">
+        <v>-6.198549562288546</v>
+      </c>
+      <c r="O40">
+        <v>-1.549637390572137</v>
+      </c>
+      <c r="P40">
+        <v>-4.648912171716409</v>
+      </c>
+      <c r="Q40">
+        <v>-2.418912171716409</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1445585667353131</v>
+      </c>
+      <c r="T40">
+        <v>1.524396295105567</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.1045289668439506</v>
+      </c>
+      <c r="W40">
+        <v>0.2138384827176646</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.4181158673758024</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1728849348086067</v>
+      </c>
+      <c r="C41">
+        <v>11.43121517605026</v>
+      </c>
+      <c r="D41">
+        <v>55.89379396134221</v>
+      </c>
+      <c r="E41">
+        <v>-47.60864886930279</v>
+      </c>
+      <c r="F41">
+        <v>45.78257878529195</v>
+      </c>
+      <c r="G41">
+        <v>1.32</v>
+      </c>
+      <c r="H41">
+        <v>24</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>6.684</v>
+      </c>
+      <c r="K41">
+        <v>2.23</v>
+      </c>
+      <c r="L41">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M41">
+        <v>10.93287981392772</v>
+      </c>
+      <c r="N41">
+        <v>-6.478879813927719</v>
+      </c>
+      <c r="O41">
+        <v>-1.61971995348193</v>
+      </c>
+      <c r="P41">
+        <v>-4.859159860445789</v>
+      </c>
+      <c r="Q41">
+        <v>-2.629159860445789</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.146292313730974</v>
+      </c>
+      <c r="T41">
+        <v>1.549386398304019</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.1018487369248749</v>
+      </c>
+      <c r="W41">
+        <v>0.2144785216223399</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.4073949476994998</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1748849348086067</v>
+      </c>
+      <c r="C42">
+        <v>9.435848356575619</v>
+      </c>
+      <c r="D42">
+        <v>55.07233941841352</v>
+      </c>
+      <c r="E42">
+        <v>-46.43473659275684</v>
+      </c>
+      <c r="F42">
+        <v>46.9564910618379</v>
+      </c>
+      <c r="G42">
+        <v>1.32</v>
+      </c>
+      <c r="H42">
+        <v>24</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>6.684</v>
+      </c>
+      <c r="K42">
+        <v>2.23</v>
+      </c>
+      <c r="L42">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M42">
+        <v>11.21321006556689</v>
+      </c>
+      <c r="N42">
+        <v>-6.75921006556689</v>
+      </c>
+      <c r="O42">
+        <v>-1.689802516391723</v>
+      </c>
+      <c r="P42">
+        <v>-5.069407549175168</v>
+      </c>
+      <c r="Q42">
+        <v>-2.839407549175168</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1480838522931569</v>
+      </c>
+      <c r="T42">
+        <v>1.575209504942419</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.09930251850175309</v>
+      </c>
+      <c r="W42">
+        <v>0.2150865585817814</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.3972100740070124</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1768849348086067</v>
+      </c>
+      <c r="C43">
+        <v>7.46427716821939</v>
+      </c>
+      <c r="D43">
+        <v>54.27468050660324</v>
+      </c>
+      <c r="E43">
+        <v>-45.26082431621089</v>
+      </c>
+      <c r="F43">
+        <v>48.13040333838385</v>
+      </c>
+      <c r="G43">
+        <v>1.32</v>
+      </c>
+      <c r="H43">
+        <v>24</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>6.684</v>
+      </c>
+      <c r="K43">
+        <v>2.23</v>
+      </c>
+      <c r="L43">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M43">
+        <v>11.49354031720606</v>
+      </c>
+      <c r="N43">
+        <v>-7.039540317206063</v>
+      </c>
+      <c r="O43">
+        <v>-1.759885079301516</v>
+      </c>
+      <c r="P43">
+        <v>-5.279655237904548</v>
+      </c>
+      <c r="Q43">
+        <v>-3.049655237904548</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1499361209760918</v>
+      </c>
+      <c r="T43">
+        <v>1.601907971127884</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.09688050585536886</v>
+      </c>
+      <c r="W43">
+        <v>0.2156649352017379</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.3875220234214755</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1788849348086067</v>
+      </c>
+      <c r="C44">
+        <v>5.515482416541396</v>
+      </c>
+      <c r="D44">
+        <v>53.49979803147119</v>
+      </c>
+      <c r="E44">
+        <v>-44.08691203966495</v>
+      </c>
+      <c r="F44">
+        <v>49.30431561492979</v>
+      </c>
+      <c r="G44">
+        <v>1.32</v>
+      </c>
+      <c r="H44">
+        <v>24</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>6.684</v>
+      </c>
+      <c r="K44">
+        <v>2.23</v>
+      </c>
+      <c r="L44">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M44">
+        <v>11.77387056884523</v>
+      </c>
+      <c r="N44">
+        <v>-7.319870568845234</v>
+      </c>
+      <c r="O44">
+        <v>-1.829967642211308</v>
+      </c>
+      <c r="P44">
+        <v>-5.489902926633926</v>
+      </c>
+      <c r="Q44">
+        <v>-3.259902926633926</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1518522609929209</v>
+      </c>
+      <c r="T44">
+        <v>1.629527074078365</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.09457382714452676</v>
+      </c>
+      <c r="W44">
+        <v>0.216215770077887</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.378295308578107</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1808849348086067</v>
+      </c>
+      <c r="C45">
+        <v>3.588502292182625</v>
+      </c>
+      <c r="D45">
+        <v>52.74673018365836</v>
+      </c>
+      <c r="E45">
+        <v>-42.912999763119</v>
+      </c>
+      <c r="F45">
+        <v>50.47822789147574</v>
+      </c>
+      <c r="G45">
+        <v>1.32</v>
+      </c>
+      <c r="H45">
+        <v>24</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>6.684</v>
+      </c>
+      <c r="K45">
+        <v>2.23</v>
+      </c>
+      <c r="L45">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M45">
+        <v>12.05420082048441</v>
+      </c>
+      <c r="N45">
+        <v>-7.600200820484407</v>
+      </c>
+      <c r="O45">
+        <v>-1.900050205121102</v>
+      </c>
+      <c r="P45">
+        <v>-5.700150615363305</v>
+      </c>
+      <c r="Q45">
+        <v>-3.470150615363305</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1538356339927967</v>
+      </c>
+      <c r="T45">
+        <v>1.658115268360441</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.09237443581558427</v>
+      </c>
+      <c r="W45">
+        <v>0.2167409847272385</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.3694977432623371</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1828849348086067</v>
+      </c>
+      <c r="C46">
+        <v>1.682428388139343</v>
+      </c>
+      <c r="D46">
+        <v>52.01456855616103</v>
+      </c>
+      <c r="E46">
+        <v>-41.73908748657306</v>
+      </c>
+      <c r="F46">
+        <v>51.65214016802169</v>
+      </c>
+      <c r="G46">
+        <v>1.32</v>
+      </c>
+      <c r="H46">
+        <v>24</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>6.684</v>
+      </c>
+      <c r="K46">
+        <v>2.23</v>
+      </c>
+      <c r="L46">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M46">
+        <v>12.33453107212358</v>
+      </c>
+      <c r="N46">
+        <v>-7.88053107212358</v>
+      </c>
+      <c r="O46">
+        <v>-1.970132768030895</v>
+      </c>
+      <c r="P46">
+        <v>-5.910398304092684</v>
+      </c>
+      <c r="Q46">
+        <v>-3.680398304092684</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1558898417426681</v>
+      </c>
+      <c r="T46">
+        <v>1.687724469581164</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.09027501681977554</v>
+      </c>
+      <c r="W46">
+        <v>0.2172423259834376</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.3611000672791022</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1848849348086067</v>
+      </c>
+      <c r="C47">
+        <v>-0.2035979558059324</v>
+      </c>
+      <c r="D47">
+        <v>51.3024544887617</v>
+      </c>
+      <c r="E47">
+        <v>-40.56517521002711</v>
+      </c>
+      <c r="F47">
+        <v>52.82605244456764</v>
+      </c>
+      <c r="G47">
+        <v>1.32</v>
+      </c>
+      <c r="H47">
+        <v>24</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>6.684</v>
+      </c>
+      <c r="K47">
+        <v>2.23</v>
+      </c>
+      <c r="L47">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M47">
+        <v>12.61486132376275</v>
+      </c>
+      <c r="N47">
+        <v>-8.160861323762752</v>
+      </c>
+      <c r="O47">
+        <v>-2.040215330940688</v>
+      </c>
+      <c r="P47">
+        <v>-6.120645992822064</v>
+      </c>
+      <c r="Q47">
+        <v>-3.890645992822064</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1580187479561712</v>
+      </c>
+      <c r="T47">
+        <v>1.718410369028094</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.08826890533489164</v>
+      </c>
+      <c r="W47">
+        <v>0.2177213854060279</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.3530756213395665</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1868849348086067</v>
+      </c>
+      <c r="C48">
+        <v>-2.070389012425871</v>
+      </c>
+      <c r="D48">
+        <v>50.60957570868771</v>
+      </c>
+      <c r="E48">
+        <v>-39.39126293348116</v>
+      </c>
+      <c r="F48">
+        <v>53.99996472111359</v>
+      </c>
+      <c r="G48">
+        <v>1.32</v>
+      </c>
+      <c r="H48">
+        <v>24</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>6.684</v>
+      </c>
+      <c r="K48">
+        <v>2.23</v>
+      </c>
+      <c r="L48">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M48">
+        <v>12.89519157540192</v>
+      </c>
+      <c r="N48">
+        <v>-8.441191575401923</v>
+      </c>
+      <c r="O48">
+        <v>-2.110297893850481</v>
+      </c>
+      <c r="P48">
+        <v>-6.330893681551442</v>
+      </c>
+      <c r="Q48">
+        <v>-4.100893681551442</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1602265025479521</v>
+      </c>
+      <c r="T48">
+        <v>1.750232783269355</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.08635001608848095</v>
+      </c>
+      <c r="W48">
+        <v>0.2181796161580708</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.3454000643539238</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1888849348086067</v>
+      </c>
+      <c r="C49">
+        <v>-3.918713757794578</v>
+      </c>
+      <c r="D49">
+        <v>49.93516323986496</v>
+      </c>
+      <c r="E49">
+        <v>-38.21735065693521</v>
+      </c>
+      <c r="F49">
+        <v>55.17387699765953</v>
+      </c>
+      <c r="G49">
+        <v>1.32</v>
+      </c>
+      <c r="H49">
+        <v>24</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>6.684</v>
+      </c>
+      <c r="K49">
+        <v>2.23</v>
+      </c>
+      <c r="L49">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M49">
+        <v>13.1755218270411</v>
+      </c>
+      <c r="N49">
+        <v>-8.721521827041096</v>
+      </c>
+      <c r="O49">
+        <v>-2.180380456760274</v>
+      </c>
+      <c r="P49">
+        <v>-6.541141370280823</v>
+      </c>
+      <c r="Q49">
+        <v>-4.311141370280822</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1625175686337625</v>
+      </c>
+      <c r="T49">
+        <v>1.783256043331041</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.08451278170361966</v>
+      </c>
+      <c r="W49">
+        <v>0.2186183477291756</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.3380511268144786</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1908849348086067</v>
+      </c>
+      <c r="C50">
+        <v>-5.749300718163823</v>
+      </c>
+      <c r="D50">
+        <v>49.27848855604165</v>
+      </c>
+      <c r="E50">
+        <v>-37.04343838038927</v>
+      </c>
+      <c r="F50">
+        <v>56.34778927420547</v>
+      </c>
+      <c r="G50">
+        <v>1.32</v>
+      </c>
+      <c r="H50">
+        <v>24</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>6.684</v>
+      </c>
+      <c r="K50">
+        <v>2.23</v>
+      </c>
+      <c r="L50">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M50">
+        <v>13.45585207868027</v>
+      </c>
+      <c r="N50">
+        <v>-9.001852078680267</v>
+      </c>
+      <c r="O50">
+        <v>-2.250463019670067</v>
+      </c>
+      <c r="P50">
+        <v>-6.751389059010201</v>
+      </c>
+      <c r="Q50">
+        <v>-4.5213890590102</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1648967526459503</v>
+      </c>
+      <c r="T50">
+        <v>1.817549428779715</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.08275209875146092</v>
+      </c>
+      <c r="W50">
+        <v>0.2190387988181511</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.3310083950058437</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1928849348086067</v>
+      </c>
+      <c r="C51">
+        <v>-7.562840595127064</v>
+      </c>
+      <c r="D51">
+        <v>48.63886095562436</v>
+      </c>
+      <c r="E51">
+        <v>-35.86952610384332</v>
+      </c>
+      <c r="F51">
+        <v>57.52170155075142</v>
+      </c>
+      <c r="G51">
+        <v>1.32</v>
+      </c>
+      <c r="H51">
+        <v>24</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>6.684</v>
+      </c>
+      <c r="K51">
+        <v>2.23</v>
+      </c>
+      <c r="L51">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M51">
+        <v>13.73618233031944</v>
+      </c>
+      <c r="N51">
+        <v>-9.28218233031944</v>
+      </c>
+      <c r="O51">
+        <v>-2.32054558257986</v>
+      </c>
+      <c r="P51">
+        <v>-6.96163674773958</v>
+      </c>
+      <c r="Q51">
+        <v>-4.73163674773958</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1673692379919493</v>
+      </c>
+      <c r="T51">
+        <v>1.853187652873435</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.08106328040959436</v>
+      </c>
+      <c r="W51">
+        <v>0.2194420886381889</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.3242531216383775</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1948849348086067</v>
+      </c>
+      <c r="C52">
+        <v>-9.359988688957564</v>
+      </c>
+      <c r="D52">
+        <v>48.01562513833981</v>
+      </c>
+      <c r="E52">
+        <v>-34.69561382729737</v>
+      </c>
+      <c r="F52">
+        <v>58.69561382729737</v>
+      </c>
+      <c r="G52">
+        <v>1.32</v>
+      </c>
+      <c r="H52">
+        <v>24</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>6.684</v>
+      </c>
+      <c r="K52">
+        <v>2.23</v>
+      </c>
+      <c r="L52">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M52">
+        <v>14.01651258195861</v>
+      </c>
+      <c r="N52">
+        <v>-9.562512581958613</v>
+      </c>
+      <c r="O52">
+        <v>-2.390628145489653</v>
+      </c>
+      <c r="P52">
+        <v>-7.171884436468959</v>
+      </c>
+      <c r="Q52">
+        <v>-4.941884436468959</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1699406227517883</v>
+      </c>
+      <c r="T52">
+        <v>1.890251405930903</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.07944201480140248</v>
+      </c>
+      <c r="W52">
+        <v>0.2198292468654251</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.3177680592056099</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1968849348086067</v>
+      </c>
+      <c r="C53">
+        <v>-11.14136713799456</v>
+      </c>
+      <c r="D53">
+        <v>47.40815896584876</v>
+      </c>
+      <c r="E53">
+        <v>-33.52170155075142</v>
+      </c>
+      <c r="F53">
+        <v>59.86952610384332</v>
+      </c>
+      <c r="G53">
+        <v>1.32</v>
+      </c>
+      <c r="H53">
+        <v>24</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>6.684</v>
+      </c>
+      <c r="K53">
+        <v>2.23</v>
+      </c>
+      <c r="L53">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M53">
+        <v>14.29684283359779</v>
+      </c>
+      <c r="N53">
+        <v>-9.842842833597786</v>
+      </c>
+      <c r="O53">
+        <v>-2.460710708399446</v>
+      </c>
+      <c r="P53">
+        <v>-7.382132125198339</v>
+      </c>
+      <c r="Q53">
+        <v>-5.152132125198339</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1726169619916207</v>
+      </c>
+      <c r="T53">
+        <v>1.928827965235615</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.07788432823666909</v>
+      </c>
+      <c r="W53">
+        <v>0.2202012224170834</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.3115373129466763</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1988849348086067</v>
+      </c>
+      <c r="C54">
+        <v>-12.90756699016439</v>
+      </c>
+      <c r="D54">
+        <v>46.81587139022488</v>
+      </c>
+      <c r="E54">
+        <v>-32.34778927420547</v>
+      </c>
+      <c r="F54">
+        <v>61.04343838038927</v>
+      </c>
+      <c r="G54">
+        <v>1.32</v>
+      </c>
+      <c r="H54">
+        <v>24</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>6.684</v>
+      </c>
+      <c r="K54">
+        <v>2.23</v>
+      </c>
+      <c r="L54">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M54">
+        <v>14.57717308523696</v>
+      </c>
+      <c r="N54">
+        <v>-10.12317308523696</v>
+      </c>
+      <c r="O54">
+        <v>-2.530793271309239</v>
+      </c>
+      <c r="P54">
+        <v>-7.592379813927717</v>
+      </c>
+      <c r="Q54">
+        <v>-5.362379813927717</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1754048153664461</v>
+      </c>
+      <c r="T54">
+        <v>1.969011881178024</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.07638655269365623</v>
+      </c>
+      <c r="W54">
+        <v>0.2205588912167549</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.305546210774625</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2008849348086067</v>
+      </c>
+      <c r="C55">
+        <v>-14.65915012113621</v>
+      </c>
+      <c r="D55">
+        <v>46.23820053579901</v>
+      </c>
+      <c r="E55">
+        <v>-31.17387699765953</v>
+      </c>
+      <c r="F55">
+        <v>62.21735065693522</v>
+      </c>
+      <c r="G55">
+        <v>1.32</v>
+      </c>
+      <c r="H55">
+        <v>24</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>6.684</v>
+      </c>
+      <c r="K55">
+        <v>2.23</v>
+      </c>
+      <c r="L55">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M55">
+        <v>14.85750333687613</v>
+      </c>
+      <c r="N55">
+        <v>-10.40350333687613</v>
+      </c>
+      <c r="O55">
+        <v>-2.600875834219032</v>
+      </c>
+      <c r="P55">
+        <v>-7.802627502657097</v>
+      </c>
+      <c r="Q55">
+        <v>-5.572627502657097</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1783113007997748</v>
+      </c>
+      <c r="T55">
+        <v>2.010905750990323</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.07494529698245517</v>
+      </c>
+      <c r="W55">
+        <v>0.2209030630805897</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.2997811879298207</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2028849348086067</v>
+      </c>
+      <c r="C56">
+        <v>-16.39665101219735</v>
+      </c>
+      <c r="D56">
+        <v>45.67461192128382</v>
+      </c>
+      <c r="E56">
+        <v>-29.99996472111358</v>
+      </c>
+      <c r="F56">
+        <v>63.39126293348117</v>
+      </c>
+      <c r="G56">
+        <v>1.32</v>
+      </c>
+      <c r="H56">
+        <v>24</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>6.684</v>
+      </c>
+      <c r="K56">
+        <v>2.23</v>
+      </c>
+      <c r="L56">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M56">
+        <v>15.1378335885153</v>
+      </c>
+      <c r="N56">
+        <v>-10.6838335885153</v>
+      </c>
+      <c r="O56">
+        <v>-2.670958397128826</v>
+      </c>
+      <c r="P56">
+        <v>-8.012875191386478</v>
+      </c>
+      <c r="Q56">
+        <v>-5.782875191386477</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1813441551649873</v>
+      </c>
+      <c r="T56">
+        <v>2.054621093403156</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.07355742111240969</v>
+      </c>
+      <c r="W56">
+        <v>0.2212344878383566</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.2942296844496388</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2048849348086067</v>
+      </c>
+      <c r="C57">
+        <v>-18.12057839967337</v>
+      </c>
+      <c r="D57">
+        <v>45.12459681035375</v>
+      </c>
+      <c r="E57">
+        <v>-28.82605244456762</v>
+      </c>
+      <c r="F57">
+        <v>64.56517521002712</v>
+      </c>
+      <c r="G57">
+        <v>1.32</v>
+      </c>
+      <c r="H57">
+        <v>24</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>6.684</v>
+      </c>
+      <c r="K57">
+        <v>2.23</v>
+      </c>
+      <c r="L57">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M57">
+        <v>15.41816384015448</v>
+      </c>
+      <c r="N57">
+        <v>-10.96416384015448</v>
+      </c>
+      <c r="O57">
+        <v>-2.741040960038619</v>
+      </c>
+      <c r="P57">
+        <v>-8.223122880115858</v>
+      </c>
+      <c r="Q57">
+        <v>-5.993122880115857</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1845118030575425</v>
+      </c>
+      <c r="T57">
+        <v>2.100279339923226</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.07222001345582042</v>
+      </c>
+      <c r="W57">
+        <v>0.2215538607867501</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.2888800538232816</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2068849348086067</v>
+      </c>
+      <c r="C58">
+        <v>-19.83141680659187</v>
+      </c>
+      <c r="D58">
+        <v>44.5876706799812</v>
+      </c>
+      <c r="E58">
+        <v>-27.65214016802167</v>
+      </c>
+      <c r="F58">
+        <v>65.73908748657307</v>
+      </c>
+      <c r="G58">
+        <v>1.32</v>
+      </c>
+      <c r="H58">
+        <v>24</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>6.684</v>
+      </c>
+      <c r="K58">
+        <v>2.23</v>
+      </c>
+      <c r="L58">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M58">
+        <v>15.69849409179365</v>
+      </c>
+      <c r="N58">
+        <v>-11.24449409179365</v>
+      </c>
+      <c r="O58">
+        <v>-2.811123522948412</v>
+      </c>
+      <c r="P58">
+        <v>-8.433370568845238</v>
+      </c>
+      <c r="Q58">
+        <v>-6.203370568845237</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1878234349452139</v>
+      </c>
+      <c r="T58">
+        <v>2.148012961285117</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.07093037035839506</v>
+      </c>
+      <c r="W58">
+        <v>0.2218618275584153</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.2837214814335802</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2088849348086067</v>
+      </c>
+      <c r="C59">
+        <v>-21.52962796628294</v>
+      </c>
+      <c r="D59">
+        <v>44.06337179683608</v>
+      </c>
+      <c r="E59">
+        <v>-26.47822789147573</v>
+      </c>
+      <c r="F59">
+        <v>66.91299976311902</v>
+      </c>
+      <c r="G59">
+        <v>1.32</v>
+      </c>
+      <c r="H59">
+        <v>24</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>6.684</v>
+      </c>
+      <c r="K59">
+        <v>2.23</v>
+      </c>
+      <c r="L59">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M59">
+        <v>15.97882434343282</v>
+      </c>
+      <c r="N59">
+        <v>-11.52482434343282</v>
+      </c>
+      <c r="O59">
+        <v>-2.881206085858206</v>
+      </c>
+      <c r="P59">
+        <v>-8.643618257574616</v>
+      </c>
+      <c r="Q59">
+        <v>-6.413618257574615</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1912890962230097</v>
+      </c>
+      <c r="T59">
+        <v>2.197966751082446</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.06968597789596706</v>
+      </c>
+      <c r="W59">
+        <v>0.2221589884784431</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.2787439115838682</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2108849348086066</v>
+      </c>
+      <c r="C60">
+        <v>-23.21565214670752</v>
+      </c>
+      <c r="D60">
+        <v>43.55125989295743</v>
+      </c>
+      <c r="E60">
+        <v>-25.30431561492979</v>
+      </c>
+      <c r="F60">
+        <v>68.08691203966495</v>
+      </c>
+      <c r="G60">
+        <v>1.32</v>
+      </c>
+      <c r="H60">
+        <v>24</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>6.684</v>
+      </c>
+      <c r="K60">
+        <v>2.23</v>
+      </c>
+      <c r="L60">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M60">
+        <v>16.25915459507199</v>
+      </c>
+      <c r="N60">
+        <v>-11.80515459507199</v>
+      </c>
+      <c r="O60">
+        <v>-2.951288648767997</v>
+      </c>
+      <c r="P60">
+        <v>-8.853865946303992</v>
+      </c>
+      <c r="Q60">
+        <v>-6.623865946303992</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1949197889902241</v>
+      </c>
+      <c r="T60">
+        <v>2.250299292774884</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.06848449551845041</v>
+      </c>
+      <c r="W60">
+        <v>0.2224459024701941</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.2739379820738016</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2128849348086067</v>
+      </c>
+      <c r="C61">
+        <v>-24.88990938349762</v>
+      </c>
+      <c r="D61">
+        <v>43.05091493271328</v>
+      </c>
+      <c r="E61">
+        <v>-24.13040333838384</v>
+      </c>
+      <c r="F61">
+        <v>69.2608243162109</v>
+      </c>
+      <c r="G61">
+        <v>1.32</v>
+      </c>
+      <c r="H61">
+        <v>24</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>6.684</v>
+      </c>
+      <c r="K61">
+        <v>2.23</v>
+      </c>
+      <c r="L61">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M61">
+        <v>16.53948484671117</v>
+      </c>
+      <c r="N61">
+        <v>-12.08548484671116</v>
+      </c>
+      <c r="O61">
+        <v>-3.021371211677791</v>
+      </c>
+      <c r="P61">
+        <v>-9.064113635033372</v>
+      </c>
+      <c r="Q61">
+        <v>-6.834113635033372</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.198727588721693</v>
+      </c>
+      <c r="T61">
+        <v>2.30518464137915</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.06732374135712073</v>
+      </c>
+      <c r="W61">
+        <v>0.2227230905639196</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.269294965428483</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2148849348086067</v>
+      </c>
+      <c r="C62">
+        <v>-26.55280062896564</v>
+      </c>
+      <c r="D62">
+        <v>42.56193596379121</v>
+      </c>
+      <c r="E62">
+        <v>-22.95649106183789</v>
+      </c>
+      <c r="F62">
+        <v>70.43473659275685</v>
+      </c>
+      <c r="G62">
+        <v>1.32</v>
+      </c>
+      <c r="H62">
+        <v>24</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>6.684</v>
+      </c>
+      <c r="K62">
+        <v>2.23</v>
+      </c>
+      <c r="L62">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M62">
+        <v>16.81981509835034</v>
+      </c>
+      <c r="N62">
+        <v>-12.36581509835034</v>
+      </c>
+      <c r="O62">
+        <v>-3.091453774587584</v>
+      </c>
+      <c r="P62">
+        <v>-9.274361323762751</v>
+      </c>
+      <c r="Q62">
+        <v>-7.04436132376275</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2027257784397353</v>
+      </c>
+      <c r="T62">
+        <v>2.362814257413629</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.06620167900116873</v>
+      </c>
+      <c r="W62">
+        <v>0.2229910390545209</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.2648067160046749</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2168849348086067</v>
+      </c>
+      <c r="C63">
+        <v>-28.20470882369001</v>
+      </c>
+      <c r="D63">
+        <v>42.08394004561278</v>
+      </c>
+      <c r="E63">
+        <v>-21.78257878529195</v>
+      </c>
+      <c r="F63">
+        <v>71.6086488693028</v>
+      </c>
+      <c r="G63">
+        <v>1.32</v>
+      </c>
+      <c r="H63">
+        <v>24</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>6.684</v>
+      </c>
+      <c r="K63">
+        <v>2.23</v>
+      </c>
+      <c r="L63">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M63">
+        <v>17.10014534998951</v>
+      </c>
+      <c r="N63">
+        <v>-12.64614534998951</v>
+      </c>
+      <c r="O63">
+        <v>-3.161536337497378</v>
+      </c>
+      <c r="P63">
+        <v>-9.484609012492133</v>
+      </c>
+      <c r="Q63">
+        <v>-7.254609012492132</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2069290035279337</v>
+      </c>
+      <c r="T63">
+        <v>2.423399238372953</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.06511640557492004</v>
+      </c>
+      <c r="W63">
+        <v>0.2232502023487091</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.2604656222996802</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2188849348086067</v>
+      </c>
+      <c r="C64">
+        <v>-29.84599989669486</v>
+      </c>
+      <c r="D64">
+        <v>41.61656124915388</v>
+      </c>
+      <c r="E64">
+        <v>-20.608666508746</v>
+      </c>
+      <c r="F64">
+        <v>72.78256114584875</v>
+      </c>
+      <c r="G64">
+        <v>1.32</v>
+      </c>
+      <c r="H64">
+        <v>24</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>6.684</v>
+      </c>
+      <c r="K64">
+        <v>2.23</v>
+      </c>
+      <c r="L64">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M64">
+        <v>17.38047560162868</v>
+      </c>
+      <c r="N64">
+        <v>-12.92647560162868</v>
+      </c>
+      <c r="O64">
+        <v>-3.23161890040717</v>
+      </c>
+      <c r="P64">
+        <v>-9.694856701221511</v>
+      </c>
+      <c r="Q64">
+        <v>-7.46485670122151</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2113534509891951</v>
+      </c>
+      <c r="T64">
+        <v>2.487172902540662</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.06406614096887296</v>
+      </c>
+      <c r="W64">
+        <v>0.2235010055366332</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.2562645638754918</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2208849348086067</v>
+      </c>
+      <c r="C65">
+        <v>-31.47702369971496</v>
+      </c>
+      <c r="D65">
+        <v>41.15944972267974</v>
+      </c>
+      <c r="E65">
+        <v>-19.43475423220005</v>
+      </c>
+      <c r="F65">
+        <v>73.95647342239469</v>
+      </c>
+      <c r="G65">
+        <v>1.32</v>
+      </c>
+      <c r="H65">
+        <v>24</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>6.684</v>
+      </c>
+      <c r="K65">
+        <v>2.23</v>
+      </c>
+      <c r="L65">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M65">
+        <v>17.66080585326785</v>
+      </c>
+      <c r="N65">
+        <v>-13.20680585326785</v>
+      </c>
+      <c r="O65">
+        <v>-3.301701463316963</v>
+      </c>
+      <c r="P65">
+        <v>-9.905104389950889</v>
+      </c>
+      <c r="Q65">
+        <v>-7.675104389950889</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2160170577726869</v>
+      </c>
+      <c r="T65">
+        <v>2.554393791798518</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.06304921809635117</v>
+      </c>
+      <c r="W65">
+        <v>0.2237438467185914</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.2521968723854047</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2228849348086067</v>
+      </c>
+      <c r="C66">
+        <v>-33.09811488055824</v>
+      </c>
+      <c r="D66">
+        <v>40.7122708183824</v>
+      </c>
+      <c r="E66">
+        <v>-18.2608419556541</v>
+      </c>
+      <c r="F66">
+        <v>75.13038569894064</v>
+      </c>
+      <c r="G66">
+        <v>1.32</v>
+      </c>
+      <c r="H66">
+        <v>24</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>6.684</v>
+      </c>
+      <c r="K66">
+        <v>2.23</v>
+      </c>
+      <c r="L66">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M66">
+        <v>17.94113610490703</v>
+      </c>
+      <c r="N66">
+        <v>-13.48713610490703</v>
+      </c>
+      <c r="O66">
+        <v>-3.371784026226757</v>
+      </c>
+      <c r="P66">
+        <v>-10.11535207868027</v>
+      </c>
+      <c r="Q66">
+        <v>-7.88535207868027</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2209397538219282</v>
+      </c>
+      <c r="T66">
+        <v>2.625349174904032</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.06206407406359567</v>
+      </c>
+      <c r="W66">
+        <v>0.2239790991136134</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.2482562962543827</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2248849348086067</v>
+      </c>
+      <c r="C67">
+        <v>-34.70959370014817</v>
+      </c>
+      <c r="D67">
+        <v>40.27470427533842</v>
+      </c>
+      <c r="E67">
+        <v>-17.08692967910815</v>
+      </c>
+      <c r="F67">
+        <v>76.30429797548659</v>
+      </c>
+      <c r="G67">
+        <v>1.32</v>
+      </c>
+      <c r="H67">
+        <v>24</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>6.684</v>
+      </c>
+      <c r="K67">
+        <v>2.23</v>
+      </c>
+      <c r="L67">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M67">
+        <v>18.2214663565462</v>
+      </c>
+      <c r="N67">
+        <v>-13.7674663565462</v>
+      </c>
+      <c r="O67">
+        <v>-3.441866589136549</v>
+      </c>
+      <c r="P67">
+        <v>-10.32559976740965</v>
+      </c>
+      <c r="Q67">
+        <v>-8.095599767409649</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.226143746788269</v>
+      </c>
+      <c r="T67">
+        <v>2.700359151329862</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.06110924215492498</v>
+      </c>
+      <c r="W67">
+        <v>0.2242071129734039</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.2444369686196999</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2268849348086067</v>
+      </c>
+      <c r="C68">
+        <v>-36.3117667974379</v>
+      </c>
+      <c r="D68">
+        <v>39.84644345459463</v>
+      </c>
+      <c r="E68">
+        <v>-15.9130174025622</v>
+      </c>
+      <c r="F68">
+        <v>77.47821025203254</v>
+      </c>
+      <c r="G68">
+        <v>1.32</v>
+      </c>
+      <c r="H68">
+        <v>24</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>6.684</v>
+      </c>
+      <c r="K68">
+        <v>2.23</v>
+      </c>
+      <c r="L68">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M68">
+        <v>18.50179660818537</v>
+      </c>
+      <c r="N68">
+        <v>-14.04779660818537</v>
+      </c>
+      <c r="O68">
+        <v>-3.511949152046343</v>
+      </c>
+      <c r="P68">
+        <v>-10.53584745613903</v>
+      </c>
+      <c r="Q68">
+        <v>-8.305847456139029</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2316538569879239</v>
+      </c>
+      <c r="T68">
+        <v>2.779781479310152</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.06018334454651701</v>
+      </c>
+      <c r="W68">
+        <v>0.2244282173222918</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.2407333781860681</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2288849348086067</v>
+      </c>
+      <c r="C69">
+        <v>-37.90492790603585</v>
+      </c>
+      <c r="D69">
+        <v>39.42719462254264</v>
+      </c>
+      <c r="E69">
+        <v>-14.73910512601626</v>
+      </c>
+      <c r="F69">
+        <v>78.65212252857849</v>
+      </c>
+      <c r="G69">
+        <v>1.32</v>
+      </c>
+      <c r="H69">
+        <v>24</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>6.684</v>
+      </c>
+      <c r="K69">
+        <v>2.23</v>
+      </c>
+      <c r="L69">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M69">
+        <v>18.78212685982454</v>
+      </c>
+      <c r="N69">
+        <v>-14.32812685982454</v>
+      </c>
+      <c r="O69">
+        <v>-3.582031714956136</v>
+      </c>
+      <c r="P69">
+        <v>-10.74609514486841</v>
+      </c>
+      <c r="Q69">
+        <v>-8.516095144868407</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2374979132602853</v>
+      </c>
+      <c r="T69">
+        <v>2.86401728171349</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.05928508567268841</v>
+      </c>
+      <c r="W69">
+        <v>0.224642721541362</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.2371403426907537</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2308849348086067</v>
+      </c>
+      <c r="C70">
+        <v>-39.48935852606176</v>
+      </c>
+      <c r="D70">
+        <v>39.01667627906267</v>
+      </c>
+      <c r="E70">
+        <v>-13.56519284947031</v>
+      </c>
+      <c r="F70">
+        <v>79.82603480512444</v>
+      </c>
+      <c r="G70">
+        <v>1.32</v>
+      </c>
+      <c r="H70">
+        <v>24</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>6.684</v>
+      </c>
+      <c r="K70">
+        <v>2.23</v>
+      </c>
+      <c r="L70">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M70">
+        <v>19.06245711146371</v>
+      </c>
+      <c r="N70">
+        <v>-14.60845711146371</v>
+      </c>
+      <c r="O70">
+        <v>-3.652114277865929</v>
+      </c>
+      <c r="P70">
+        <v>-10.95634283359779</v>
+      </c>
+      <c r="Q70">
+        <v>-8.726342833597785</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2437072230496692</v>
+      </c>
+      <c r="T70">
+        <v>2.953517821767037</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.05841324617750181</v>
+      </c>
+      <c r="W70">
+        <v>0.2248509168128126</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.2336529847100073</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2328849348086067</v>
+      </c>
+      <c r="C71">
+        <v>-41.06532855446299</v>
+      </c>
+      <c r="D71">
+        <v>38.6146185272074</v>
+      </c>
+      <c r="E71">
+        <v>-12.39128057292436</v>
+      </c>
+      <c r="F71">
+        <v>80.99994708167038</v>
+      </c>
+      <c r="G71">
+        <v>1.32</v>
+      </c>
+      <c r="H71">
+        <v>24</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>6.684</v>
+      </c>
+      <c r="K71">
+        <v>2.23</v>
+      </c>
+      <c r="L71">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M71">
+        <v>19.34278736310289</v>
+      </c>
+      <c r="N71">
+        <v>-14.88878736310289</v>
+      </c>
+      <c r="O71">
+        <v>-3.722196840775722</v>
+      </c>
+      <c r="P71">
+        <v>-11.16659052232717</v>
+      </c>
+      <c r="Q71">
+        <v>-8.936590522327165</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2503171334706263</v>
+      </c>
+      <c r="T71">
+        <v>3.048792590211135</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.05756667739232062</v>
+      </c>
+      <c r="W71">
+        <v>0.2250530774387139</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.2302667095692825</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2348849348086067</v>
+      </c>
+      <c r="C72">
+        <v>-42.63309687675664</v>
+      </c>
+      <c r="D72">
+        <v>38.22076248145969</v>
+      </c>
+      <c r="E72">
+        <v>-11.21736829637841</v>
+      </c>
+      <c r="F72">
+        <v>82.17385935821633</v>
+      </c>
+      <c r="G72">
+        <v>1.32</v>
+      </c>
+      <c r="H72">
+        <v>24</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>6.684</v>
+      </c>
+      <c r="K72">
+        <v>2.23</v>
+      </c>
+      <c r="L72">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M72">
+        <v>19.62311761474206</v>
+      </c>
+      <c r="N72">
+        <v>-15.16911761474206</v>
+      </c>
+      <c r="O72">
+        <v>-3.792279403685515</v>
+      </c>
+      <c r="P72">
+        <v>-11.37683821105654</v>
+      </c>
+      <c r="Q72">
+        <v>-9.146838211056544</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2573677045863138</v>
+      </c>
+      <c r="T72">
+        <v>3.150419009884839</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.05674429628671605</v>
+      </c>
+      <c r="W72">
+        <v>0.2252494620467322</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.2269771851468642</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2368849348086067</v>
+      </c>
+      <c r="C73">
+        <v>-44.19291192292399</v>
+      </c>
+      <c r="D73">
+        <v>37.83485971183828</v>
+      </c>
+      <c r="E73">
+        <v>-10.04345601983248</v>
+      </c>
+      <c r="F73">
+        <v>83.34777163476227</v>
+      </c>
+      <c r="G73">
+        <v>1.32</v>
+      </c>
+      <c r="H73">
+        <v>24</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>6.684</v>
+      </c>
+      <c r="K73">
+        <v>2.23</v>
+      </c>
+      <c r="L73">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M73">
+        <v>19.90344786638123</v>
+      </c>
+      <c r="N73">
+        <v>-15.44944786638123</v>
+      </c>
+      <c r="O73">
+        <v>-3.862361966595308</v>
+      </c>
+      <c r="P73">
+        <v>-11.58708589978592</v>
+      </c>
+      <c r="Q73">
+        <v>-9.357085899785922</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2649045219858418</v>
+      </c>
+      <c r="T73">
+        <v>3.259054148156729</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.05594508084605808</v>
+      </c>
+      <c r="W73">
+        <v>0.2254403146939613</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.2237803233842323</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2388849348086067</v>
+      </c>
+      <c r="C74">
+        <v>-45.74501218996538</v>
+      </c>
+      <c r="D74">
+        <v>37.45667172134284</v>
+      </c>
+      <c r="E74">
+        <v>-8.869543743286528</v>
+      </c>
+      <c r="F74">
+        <v>84.52168391130822</v>
+      </c>
+      <c r="G74">
+        <v>1.32</v>
+      </c>
+      <c r="H74">
+        <v>24</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>6.684</v>
+      </c>
+      <c r="K74">
+        <v>2.23</v>
+      </c>
+      <c r="L74">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M74">
+        <v>20.1837781180204</v>
+      </c>
+      <c r="N74">
+        <v>-15.7297781180204</v>
+      </c>
+      <c r="O74">
+        <v>-3.9324445295051</v>
+      </c>
+      <c r="P74">
+        <v>-11.7973335885153</v>
+      </c>
+      <c r="Q74">
+        <v>-9.5673335885153</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2729796834853362</v>
+      </c>
+      <c r="T74">
+        <v>3.375448939162327</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.05516806583430727</v>
+      </c>
+      <c r="W74">
+        <v>0.2256258658787675</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.2206722633372291</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2408849348086067</v>
+      </c>
+      <c r="C75">
+        <v>-47.28962673342515</v>
+      </c>
+      <c r="D75">
+        <v>37.08596945442901</v>
+      </c>
+      <c r="E75">
+        <v>-7.695631466740579</v>
+      </c>
+      <c r="F75">
+        <v>85.69559618785416</v>
+      </c>
+      <c r="G75">
+        <v>1.32</v>
+      </c>
+      <c r="H75">
+        <v>24</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>6.684</v>
+      </c>
+      <c r="K75">
+        <v>2.23</v>
+      </c>
+      <c r="L75">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M75">
+        <v>20.46410836965958</v>
+      </c>
+      <c r="N75">
+        <v>-16.01010836965958</v>
+      </c>
+      <c r="O75">
+        <v>-4.002527092414894</v>
+      </c>
+      <c r="P75">
+        <v>-12.00758127724468</v>
+      </c>
+      <c r="Q75">
+        <v>-9.777581277244682</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2816530050959042</v>
+      </c>
+      <c r="T75">
+        <v>3.500465566538709</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.05441233890507018</v>
+      </c>
+      <c r="W75">
+        <v>0.2258063334694693</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.2176493556202808</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2428849348086067</v>
+      </c>
+      <c r="C76">
+        <v>-48.82697563001568</v>
+      </c>
+      <c r="D76">
+        <v>36.72253283438443</v>
+      </c>
+      <c r="E76">
+        <v>-6.521719190194631</v>
+      </c>
+      <c r="F76">
+        <v>86.86950846440011</v>
+      </c>
+      <c r="G76">
+        <v>1.32</v>
+      </c>
+      <c r="H76">
+        <v>24</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>6.684</v>
+      </c>
+      <c r="K76">
+        <v>2.23</v>
+      </c>
+      <c r="L76">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M76">
+        <v>20.74443862129875</v>
+      </c>
+      <c r="N76">
+        <v>-16.29043862129875</v>
+      </c>
+      <c r="O76">
+        <v>-4.072609655324687</v>
+      </c>
+      <c r="P76">
+        <v>-12.21782896597406</v>
+      </c>
+      <c r="Q76">
+        <v>-9.98782896597406</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2909935052919005</v>
+      </c>
+      <c r="T76">
+        <v>3.635098857559429</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.05367703702797464</v>
+      </c>
+      <c r="W76">
+        <v>0.2259819235577196</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.2147081481118985</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2448849348086067</v>
+      </c>
+      <c r="C77">
+        <v>-50.35727041330323</v>
+      </c>
+      <c r="D77">
+        <v>36.36615032764283</v>
+      </c>
+      <c r="E77">
+        <v>-5.347806913648682</v>
+      </c>
+      <c r="F77">
+        <v>88.04342074094606</v>
+      </c>
+      <c r="G77">
+        <v>1.32</v>
+      </c>
+      <c r="H77">
+        <v>24</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>6.684</v>
+      </c>
+      <c r="K77">
+        <v>2.23</v>
+      </c>
+      <c r="L77">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M77">
+        <v>21.02476887293792</v>
+      </c>
+      <c r="N77">
+        <v>-16.57076887293792</v>
+      </c>
+      <c r="O77">
+        <v>-4.14269221823448</v>
+      </c>
+      <c r="P77">
+        <v>-12.42807665470344</v>
+      </c>
+      <c r="Q77">
+        <v>-10.19807665470344</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3010812455035765</v>
+      </c>
+      <c r="T77">
+        <v>3.780502811861806</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.05296134320093498</v>
+      </c>
+      <c r="W77">
+        <v>0.2261528312436167</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.2118453728037399</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2468849348086067</v>
+      </c>
+      <c r="C78">
+        <v>-51.88071448426852</v>
+      </c>
+      <c r="D78">
+        <v>36.01661853322349</v>
+      </c>
+      <c r="E78">
+        <v>-4.173894637102734</v>
+      </c>
+      <c r="F78">
+        <v>89.21733301749201</v>
+      </c>
+      <c r="G78">
+        <v>1.32</v>
+      </c>
+      <c r="H78">
+        <v>24</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>6.684</v>
+      </c>
+      <c r="K78">
+        <v>2.23</v>
+      </c>
+      <c r="L78">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M78">
+        <v>21.30509912457709</v>
+      </c>
+      <c r="N78">
+        <v>-16.85109912457709</v>
+      </c>
+      <c r="O78">
+        <v>-4.212774781144273</v>
+      </c>
+      <c r="P78">
+        <v>-12.63832434343282</v>
+      </c>
+      <c r="Q78">
+        <v>-10.40832434343282</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3120096307328922</v>
+      </c>
+      <c r="T78">
+        <v>3.938023762356048</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.05226448342197531</v>
+      </c>
+      <c r="W78">
+        <v>0.2263192413588323</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.2090579336879013</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2488849348086067</v>
+      </c>
+      <c r="C79">
+        <v>-53.39750349841621</v>
+      </c>
+      <c r="D79">
+        <v>35.67374179562174</v>
+      </c>
+      <c r="E79">
+        <v>-2.999982360556785</v>
+      </c>
+      <c r="F79">
+        <v>90.39124529403796</v>
+      </c>
+      <c r="G79">
+        <v>1.32</v>
+      </c>
+      <c r="H79">
+        <v>24</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>6.684</v>
+      </c>
+      <c r="K79">
+        <v>2.23</v>
+      </c>
+      <c r="L79">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M79">
+        <v>21.58542937621626</v>
+      </c>
+      <c r="N79">
+        <v>-17.13142937621626</v>
+      </c>
+      <c r="O79">
+        <v>-4.282857344054066</v>
+      </c>
+      <c r="P79">
+        <v>-12.8485720321622</v>
+      </c>
+      <c r="Q79">
+        <v>-10.6185720321622</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3238883103299746</v>
+      </c>
+      <c r="T79">
+        <v>4.109242186806312</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.05158572389701459</v>
+      </c>
+      <c r="W79">
+        <v>0.2264813291333929</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.2063428955880584</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2508849348086067</v>
+      </c>
+      <c r="C80">
+        <v>-54.90782573098109</v>
+      </c>
+      <c r="D80">
+        <v>35.33733183960282</v>
+      </c>
+      <c r="E80">
+        <v>-1.826070084010837</v>
+      </c>
+      <c r="F80">
+        <v>91.56515757058391</v>
+      </c>
+      <c r="G80">
+        <v>1.32</v>
+      </c>
+      <c r="H80">
+        <v>24</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>6.684</v>
+      </c>
+      <c r="K80">
+        <v>2.23</v>
+      </c>
+      <c r="L80">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M80">
+        <v>21.86575962785544</v>
+      </c>
+      <c r="N80">
+        <v>-17.41175962785544</v>
+      </c>
+      <c r="O80">
+        <v>-4.35293990696386</v>
+      </c>
+      <c r="P80">
+        <v>-13.05881972089158</v>
+      </c>
+      <c r="Q80">
+        <v>-10.82881972089158</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3368468698904279</v>
+      </c>
+      <c r="T80">
+        <v>4.296025922570235</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.05092436846243747</v>
+      </c>
+      <c r="W80">
+        <v>0.2266392608111699</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.2036974738497499</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2528849348086067</v>
+      </c>
+      <c r="C81">
+        <v>-56.41186242166383</v>
+      </c>
+      <c r="D81">
+        <v>35.00720742546602</v>
+      </c>
+      <c r="E81">
+        <v>-0.6521578074648886</v>
+      </c>
+      <c r="F81">
+        <v>92.73906984712985</v>
+      </c>
+      <c r="G81">
+        <v>1.32</v>
+      </c>
+      <c r="H81">
+        <v>24</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>6.684</v>
+      </c>
+      <c r="K81">
+        <v>2.23</v>
+      </c>
+      <c r="L81">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M81">
+        <v>22.14608987949461</v>
+      </c>
+      <c r="N81">
+        <v>-17.69208987949461</v>
+      </c>
+      <c r="O81">
+        <v>-4.423022469873652</v>
+      </c>
+      <c r="P81">
+        <v>-13.26906740962096</v>
+      </c>
+      <c r="Q81">
+        <v>-11.03906740962096</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3510395779804483</v>
+      </c>
+      <c r="T81">
+        <v>4.500598585549771</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.05027975620341928</v>
+      </c>
+      <c r="W81">
+        <v>0.2267931942186235</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.2011190248136772</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2548849348086067</v>
+      </c>
+      <c r="C82">
+        <v>-57.90978810022204</v>
+      </c>
+      <c r="D82">
+        <v>34.68319402345377</v>
+      </c>
+      <c r="E82">
+        <v>0.5217544690810598</v>
+      </c>
+      <c r="F82">
+        <v>93.9129821236758</v>
+      </c>
+      <c r="G82">
+        <v>1.32</v>
+      </c>
+      <c r="H82">
+        <v>24</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>6.684</v>
+      </c>
+      <c r="K82">
+        <v>2.23</v>
+      </c>
+      <c r="L82">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M82">
+        <v>22.42642013113378</v>
+      </c>
+      <c r="N82">
+        <v>-17.97242013113378</v>
+      </c>
+      <c r="O82">
+        <v>-4.493105032783445</v>
+      </c>
+      <c r="P82">
+        <v>-13.47931509835034</v>
+      </c>
+      <c r="Q82">
+        <v>-11.24931509835034</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3666515568794708</v>
+      </c>
+      <c r="T82">
+        <v>4.725628514827259</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.04965125925087654</v>
+      </c>
+      <c r="W82">
+        <v>0.2269432792908907</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.1986050370035062</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2568849348086067</v>
+      </c>
+      <c r="C83">
+        <v>-59.40177089414592</v>
+      </c>
+      <c r="D83">
+        <v>34.36512350607583</v>
+      </c>
+      <c r="E83">
+        <v>1.695666745627008</v>
+      </c>
+      <c r="F83">
+        <v>95.08689440022175</v>
+      </c>
+      <c r="G83">
+        <v>1.32</v>
+      </c>
+      <c r="H83">
+        <v>24</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>6.684</v>
+      </c>
+      <c r="K83">
+        <v>2.23</v>
+      </c>
+      <c r="L83">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M83">
+        <v>22.70675038277296</v>
+      </c>
+      <c r="N83">
+        <v>-18.25275038277296</v>
+      </c>
+      <c r="O83">
+        <v>-4.563187595693239</v>
+      </c>
+      <c r="P83">
+        <v>-13.68956278707972</v>
+      </c>
+      <c r="Q83">
+        <v>-11.45956278707972</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3839069019783903</v>
+      </c>
+      <c r="T83">
+        <v>4.974345805081326</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.04903828074160646</v>
+      </c>
+      <c r="W83">
+        <v>0.2270896585589044</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.1961531229664258</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2588849348086067</v>
+      </c>
+      <c r="C84">
+        <v>-60.88797281955823</v>
+      </c>
+      <c r="D84">
+        <v>34.05283385720947</v>
+      </c>
+      <c r="E84">
+        <v>2.869579022172957</v>
+      </c>
+      <c r="F84">
+        <v>96.2608066767677</v>
+      </c>
+      <c r="G84">
+        <v>1.32</v>
+      </c>
+      <c r="H84">
+        <v>24</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>6.684</v>
+      </c>
+      <c r="K84">
+        <v>2.23</v>
+      </c>
+      <c r="L84">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M84">
+        <v>22.98708063441213</v>
+      </c>
+      <c r="N84">
+        <v>-18.53308063441213</v>
+      </c>
+      <c r="O84">
+        <v>-4.633270158603032</v>
+      </c>
+      <c r="P84">
+        <v>-13.89981047580909</v>
+      </c>
+      <c r="Q84">
+        <v>-11.66981047580909</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4030795076438564</v>
+      </c>
+      <c r="T84">
+        <v>5.250698349808066</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.04844025292768443</v>
+      </c>
+      <c r="W84">
+        <v>0.227232467600869</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.1937610117107378</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2608849348086067</v>
+      </c>
+      <c r="C85">
+        <v>-62.36855005639565</v>
+      </c>
+      <c r="D85">
+        <v>33.746168896918</v>
+      </c>
+      <c r="E85">
+        <v>4.043491298718905</v>
+      </c>
+      <c r="F85">
+        <v>97.43471895331365</v>
+      </c>
+      <c r="G85">
+        <v>1.32</v>
+      </c>
+      <c r="H85">
+        <v>24</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>6.684</v>
+      </c>
+      <c r="K85">
+        <v>2.23</v>
+      </c>
+      <c r="L85">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M85">
+        <v>23.2674108860513</v>
+      </c>
+      <c r="N85">
+        <v>-18.8134108860513</v>
+      </c>
+      <c r="O85">
+        <v>-4.703352721512825</v>
+      </c>
+      <c r="P85">
+        <v>-14.11005816453848</v>
+      </c>
+      <c r="Q85">
+        <v>-11.88005816453848</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.424507713975848</v>
+      </c>
+      <c r="T85">
+        <v>5.559562958620305</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.0478566354225316</v>
+      </c>
+      <c r="W85">
+        <v>0.2273718354610995</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.1914265416901264</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2628849348086067</v>
+      </c>
+      <c r="C86">
+        <v>-63.84365320885424</v>
+      </c>
+      <c r="D86">
+        <v>33.44497802100534</v>
+      </c>
+      <c r="E86">
+        <v>5.217403575264839</v>
+      </c>
+      <c r="F86">
+        <v>98.60863122985958</v>
+      </c>
+      <c r="G86">
+        <v>1.32</v>
+      </c>
+      <c r="H86">
+        <v>24</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>6.684</v>
+      </c>
+      <c r="K86">
+        <v>2.23</v>
+      </c>
+      <c r="L86">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M86">
+        <v>23.54774113769047</v>
+      </c>
+      <c r="N86">
+        <v>-19.09374113769047</v>
+      </c>
+      <c r="O86">
+        <v>-4.773435284422617</v>
+      </c>
+      <c r="P86">
+        <v>-14.32030585326785</v>
+      </c>
+      <c r="Q86">
+        <v>-12.09030585326785</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4486144460993383</v>
+      </c>
+      <c r="T86">
+        <v>5.907035643534072</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.04728691357226338</v>
+      </c>
+      <c r="W86">
+        <v>0.2275078850389435</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.1891476542890536</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2648849348086067</v>
+      </c>
+      <c r="C87">
+        <v>-65.31342755201086</v>
+      </c>
+      <c r="D87">
+        <v>33.14911595439467</v>
+      </c>
+      <c r="E87">
+        <v>6.391315851810788</v>
+      </c>
+      <c r="F87">
+        <v>99.78254350640553</v>
+      </c>
+      <c r="G87">
+        <v>1.32</v>
+      </c>
+      <c r="H87">
+        <v>24</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>6.684</v>
+      </c>
+      <c r="K87">
+        <v>2.23</v>
+      </c>
+      <c r="L87">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M87">
+        <v>23.82807138932964</v>
+      </c>
+      <c r="N87">
+        <v>-19.37407138932964</v>
+      </c>
+      <c r="O87">
+        <v>-4.843517847332411</v>
+      </c>
+      <c r="P87">
+        <v>-14.53055354199723</v>
+      </c>
+      <c r="Q87">
+        <v>-12.30055354199723</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4759354091726275</v>
+      </c>
+      <c r="T87">
+        <v>6.300838019769676</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.04673059694200146</v>
+      </c>
+      <c r="W87">
+        <v>0.2276407334502501</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.1869223877680058</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2668849348086067</v>
+      </c>
+      <c r="C88">
+        <v>-66.77801326546934</v>
+      </c>
+      <c r="D88">
+        <v>32.85844251748214</v>
+      </c>
+      <c r="E88">
+        <v>7.565228128356736</v>
+      </c>
+      <c r="F88">
+        <v>100.9564557829515</v>
+      </c>
+      <c r="G88">
+        <v>1.32</v>
+      </c>
+      <c r="H88">
+        <v>24</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>6.684</v>
+      </c>
+      <c r="K88">
+        <v>2.23</v>
+      </c>
+      <c r="L88">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M88">
+        <v>24.10840164096881</v>
+      </c>
+      <c r="N88">
+        <v>-19.65440164096881</v>
+      </c>
+      <c r="O88">
+        <v>-4.913600410242204</v>
+      </c>
+      <c r="P88">
+        <v>-14.74080123072661</v>
+      </c>
+      <c r="Q88">
+        <v>-12.51080123072661</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.5071593669706724</v>
+      </c>
+      <c r="T88">
+        <v>6.750897878324654</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.04618721790779214</v>
+      </c>
+      <c r="W88">
+        <v>0.2277704923636193</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.1847488716311686</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2688849348086066</v>
+      </c>
+      <c r="C89">
+        <v>-68.23754565482115</v>
+      </c>
+      <c r="D89">
+        <v>32.57282240467628</v>
+      </c>
+      <c r="E89">
+        <v>8.739140404902685</v>
+      </c>
+      <c r="F89">
+        <v>102.1303680594974</v>
+      </c>
+      <c r="G89">
+        <v>1.32</v>
+      </c>
+      <c r="H89">
+        <v>24</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>6.684</v>
+      </c>
+      <c r="K89">
+        <v>2.23</v>
+      </c>
+      <c r="L89">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M89">
+        <v>24.38873189260799</v>
+      </c>
+      <c r="N89">
+        <v>-19.93473189260799</v>
+      </c>
+      <c r="O89">
+        <v>-4.983682973151996</v>
+      </c>
+      <c r="P89">
+        <v>-14.95104891945599</v>
+      </c>
+      <c r="Q89">
+        <v>-12.72104891945599</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.543187010583801</v>
+      </c>
+      <c r="T89">
+        <v>7.270197715118858</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.04565633034563361</v>
+      </c>
+      <c r="W89">
+        <v>0.2278972683134627</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.1826253213825344</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2708849348086067</v>
+      </c>
+      <c r="C90">
+        <v>-69.69215536165518</v>
+      </c>
+      <c r="D90">
+        <v>32.29212497438819</v>
+      </c>
+      <c r="E90">
+        <v>9.913052681448633</v>
+      </c>
+      <c r="F90">
+        <v>103.3042803360434</v>
+      </c>
+      <c r="G90">
+        <v>1.32</v>
+      </c>
+      <c r="H90">
+        <v>24</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>6.684</v>
+      </c>
+      <c r="K90">
+        <v>2.23</v>
+      </c>
+      <c r="L90">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M90">
+        <v>24.66906214424716</v>
+      </c>
+      <c r="N90">
+        <v>-20.21506214424716</v>
+      </c>
+      <c r="O90">
+        <v>-5.05376553606179</v>
+      </c>
+      <c r="P90">
+        <v>-15.16129660818537</v>
+      </c>
+      <c r="Q90">
+        <v>-12.93129660818537</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.5852192614657845</v>
+      </c>
+      <c r="T90">
+        <v>7.876047524712097</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.04513750840988777</v>
+      </c>
+      <c r="W90">
+        <v>0.2280211629917188</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.180550033639551</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2728849348086066</v>
+      </c>
+      <c r="C91">
+        <v>-71.14196856280176</v>
+      </c>
+      <c r="D91">
+        <v>32.01622404978755</v>
+      </c>
+      <c r="E91">
+        <v>11.08696495799458</v>
+      </c>
+      <c r="F91">
+        <v>104.4781926125893</v>
+      </c>
+      <c r="G91">
+        <v>1.32</v>
+      </c>
+      <c r="H91">
+        <v>24</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>6.684</v>
+      </c>
+      <c r="K91">
+        <v>2.23</v>
+      </c>
+      <c r="L91">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M91">
+        <v>24.94939239588633</v>
+      </c>
+      <c r="N91">
+        <v>-20.49539239588633</v>
+      </c>
+      <c r="O91">
+        <v>-5.123848098971583</v>
+      </c>
+      <c r="P91">
+        <v>-15.37154429691475</v>
+      </c>
+      <c r="Q91">
+        <v>-13.14154429691475</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.6348937397808558</v>
+      </c>
+      <c r="T91">
+        <v>8.592051845140469</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.04463034539404633</v>
+      </c>
+      <c r="W91">
+        <v>0.2281422735199017</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.1785213815761854</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2748849348086067</v>
+      </c>
+      <c r="C92">
+        <v>-72.58710715944936</v>
+      </c>
+      <c r="D92">
+        <v>31.74499772968592</v>
+      </c>
+      <c r="E92">
+        <v>12.26087723454053</v>
+      </c>
+      <c r="F92">
+        <v>105.6521048891353</v>
+      </c>
+      <c r="G92">
+        <v>1.32</v>
+      </c>
+      <c r="H92">
+        <v>24</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>6.684</v>
+      </c>
+      <c r="K92">
+        <v>2.23</v>
+      </c>
+      <c r="L92">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M92">
+        <v>25.22972264752551</v>
+      </c>
+      <c r="N92">
+        <v>-20.77572264752551</v>
+      </c>
+      <c r="O92">
+        <v>-5.193930661881376</v>
+      </c>
+      <c r="P92">
+        <v>-15.58179198564413</v>
+      </c>
+      <c r="Q92">
+        <v>-13.35179198564413</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.6945031137589415</v>
+      </c>
+      <c r="T92">
+        <v>9.451257029654517</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.04413445266744582</v>
+      </c>
+      <c r="W92">
+        <v>0.2282606927030139</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.1765378106697832</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2768849348086067</v>
+      </c>
+      <c r="C93">
+        <v>-74.02768895672921</v>
+      </c>
+      <c r="D93">
+        <v>31.47832820895201</v>
+      </c>
+      <c r="E93">
+        <v>13.43478951108648</v>
+      </c>
+      <c r="F93">
+        <v>106.8260171656812</v>
+      </c>
+      <c r="G93">
+        <v>1.32</v>
+      </c>
+      <c r="H93">
+        <v>24</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>6.684</v>
+      </c>
+      <c r="K93">
+        <v>2.23</v>
+      </c>
+      <c r="L93">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M93">
+        <v>25.51005289916468</v>
+      </c>
+      <c r="N93">
+        <v>-21.05605289916468</v>
+      </c>
+      <c r="O93">
+        <v>-5.264013224791169</v>
+      </c>
+      <c r="P93">
+        <v>-15.79203967437351</v>
+      </c>
+      <c r="Q93">
+        <v>-13.56203967437351</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.7673590152877128</v>
+      </c>
+      <c r="T93">
+        <v>10.50139669961613</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.04364945868208927</v>
+      </c>
+      <c r="W93">
+        <v>0.2283765092667171</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.1745978347283571</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2788849348086067</v>
+      </c>
+      <c r="C94">
+        <v>-75.46382783432404</v>
+      </c>
+      <c r="D94">
+        <v>31.21610160790313</v>
+      </c>
+      <c r="E94">
+        <v>14.60870178763243</v>
+      </c>
+      <c r="F94">
+        <v>107.9999294422272</v>
+      </c>
+      <c r="G94">
+        <v>1.32</v>
+      </c>
+      <c r="H94">
+        <v>24</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>6.684</v>
+      </c>
+      <c r="K94">
+        <v>2.23</v>
+      </c>
+      <c r="L94">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M94">
+        <v>25.79038315080385</v>
+      </c>
+      <c r="N94">
+        <v>-21.33638315080385</v>
+      </c>
+      <c r="O94">
+        <v>-5.334095787700962</v>
+      </c>
+      <c r="P94">
+        <v>-16.00228736310289</v>
+      </c>
+      <c r="Q94">
+        <v>-13.77228736310289</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.8584288921986771</v>
+      </c>
+      <c r="T94">
+        <v>11.81407128706815</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.04317500804424047</v>
+      </c>
+      <c r="W94">
+        <v>0.2284898080790354</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.1727000321769619</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2808849348086067</v>
+      </c>
+      <c r="C95">
+        <v>-76.8956339086198</v>
+      </c>
+      <c r="D95">
+        <v>30.95820781015331</v>
+      </c>
+      <c r="E95">
+        <v>15.78261406417838</v>
+      </c>
+      <c r="F95">
+        <v>109.1738417187731</v>
+      </c>
+      <c r="G95">
+        <v>1.32</v>
+      </c>
+      <c r="H95">
+        <v>24</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>6.684</v>
+      </c>
+      <c r="K95">
+        <v>2.23</v>
+      </c>
+      <c r="L95">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M95">
+        <v>26.07071340244302</v>
+      </c>
+      <c r="N95">
+        <v>-21.61671340244302</v>
+      </c>
+      <c r="O95">
+        <v>-5.404178350610755</v>
+      </c>
+      <c r="P95">
+        <v>-16.21253505183227</v>
+      </c>
+      <c r="Q95">
+        <v>-13.98253505183227</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.9755187339413456</v>
+      </c>
+      <c r="T95">
+        <v>13.50179575664932</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.04271076064591531</v>
+      </c>
+      <c r="W95">
+        <v>0.2286006703577554</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.1708430425836612</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2828849348086067</v>
+      </c>
+      <c r="C96">
+        <v>-78.32321368688541</v>
+      </c>
+      <c r="D96">
+        <v>30.70454030843366</v>
+      </c>
+      <c r="E96">
+        <v>16.95652634072432</v>
+      </c>
+      <c r="F96">
+        <v>110.3477539953191</v>
+      </c>
+      <c r="G96">
+        <v>1.32</v>
+      </c>
+      <c r="H96">
+        <v>24</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>6.684</v>
+      </c>
+      <c r="K96">
+        <v>2.23</v>
+      </c>
+      <c r="L96">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M96">
+        <v>26.35104365408219</v>
+      </c>
+      <c r="N96">
+        <v>-21.89704365408219</v>
+      </c>
+      <c r="O96">
+        <v>-5.474260913520548</v>
+      </c>
+      <c r="P96">
+        <v>-16.42278274056164</v>
+      </c>
+      <c r="Q96">
+        <v>-14.19278274056164</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.13163852293157</v>
+      </c>
+      <c r="T96">
+        <v>15.75209504942421</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.04225639085180983</v>
+      </c>
+      <c r="W96">
+        <v>0.2287091738645878</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.1690255634072393</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2848849348086067</v>
+      </c>
+      <c r="C97">
+        <v>-79.74667021393427</v>
+      </c>
+      <c r="D97">
+        <v>30.45499605793075</v>
+      </c>
+      <c r="E97">
+        <v>18.13043861727027</v>
+      </c>
+      <c r="F97">
+        <v>111.521666271865</v>
+      </c>
+      <c r="G97">
+        <v>1.32</v>
+      </c>
+      <c r="H97">
+        <v>24</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>6.684</v>
+      </c>
+      <c r="K97">
+        <v>2.23</v>
+      </c>
+      <c r="L97">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M97">
+        <v>26.63137390572137</v>
+      </c>
+      <c r="N97">
+        <v>-22.17737390572137</v>
+      </c>
+      <c r="O97">
+        <v>-5.544343476430342</v>
+      </c>
+      <c r="P97">
+        <v>-16.63303042929103</v>
+      </c>
+      <c r="Q97">
+        <v>-14.40303042929103</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.350206227517885</v>
+      </c>
+      <c r="T97">
+        <v>18.90251405930906</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.04181158673758024</v>
+      </c>
+      <c r="W97">
+        <v>0.2288153930870659</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.167246346950321</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2868849348086067</v>
+      </c>
+      <c r="C98">
+        <v>-81.16610321169145</v>
+      </c>
+      <c r="D98">
+        <v>30.20947533671949</v>
+      </c>
+      <c r="E98">
+        <v>19.30435089381621</v>
+      </c>
+      <c r="F98">
+        <v>112.6955785484109</v>
+      </c>
+      <c r="G98">
+        <v>1.32</v>
+      </c>
+      <c r="H98">
+        <v>24</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>6.684</v>
+      </c>
+      <c r="K98">
+        <v>2.23</v>
+      </c>
+      <c r="L98">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M98">
+        <v>26.91170415736054</v>
+      </c>
+      <c r="N98">
+        <v>-22.45770415736053</v>
+      </c>
+      <c r="O98">
+        <v>-5.614426039340134</v>
+      </c>
+      <c r="P98">
+        <v>-16.8432781180204</v>
+      </c>
+      <c r="Q98">
+        <v>-14.6132781180204</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.678057784397352</v>
+      </c>
+      <c r="T98">
+        <v>23.62814257413627</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.04137604937573046</v>
+      </c>
+      <c r="W98">
+        <v>0.2289193994090756</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.1655041975029218</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2888849348086067</v>
+      </c>
+      <c r="C99">
+        <v>-82.58160921206439</v>
+      </c>
+      <c r="D99">
+        <v>29.96788161289251</v>
+      </c>
+      <c r="E99">
+        <v>20.47826317036215</v>
+      </c>
+      <c r="F99">
+        <v>113.8694908249569</v>
+      </c>
+      <c r="G99">
+        <v>1.32</v>
+      </c>
+      <c r="H99">
+        <v>24</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>6.684</v>
+      </c>
+      <c r="K99">
+        <v>2.23</v>
+      </c>
+      <c r="L99">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M99">
+        <v>27.19203440899971</v>
+      </c>
+      <c r="N99">
+        <v>-22.73803440899971</v>
+      </c>
+      <c r="O99">
+        <v>-5.684508602249927</v>
+      </c>
+      <c r="P99">
+        <v>-17.05352580674978</v>
+      </c>
+      <c r="Q99">
+        <v>-14.82352580674978</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.224477045863136</v>
+      </c>
+      <c r="T99">
+        <v>31.50419009884836</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.04094949216567138</v>
+      </c>
+      <c r="W99">
+        <v>0.2290212612708377</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.1637979686626855</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2908849348086067</v>
+      </c>
+      <c r="C100">
+        <v>-83.99328168348788</v>
+      </c>
+      <c r="D100">
+        <v>29.73012141801497</v>
+      </c>
+      <c r="E100">
+        <v>21.6521754469081</v>
+      </c>
+      <c r="F100">
+        <v>115.0434031015028</v>
+      </c>
+      <c r="G100">
+        <v>1.32</v>
+      </c>
+      <c r="H100">
+        <v>24</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>6.684</v>
+      </c>
+      <c r="K100">
+        <v>2.23</v>
+      </c>
+      <c r="L100">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M100">
+        <v>27.47236466063888</v>
+      </c>
+      <c r="N100">
+        <v>-23.01836466063888</v>
+      </c>
+      <c r="O100">
+        <v>-5.75459116515972</v>
+      </c>
+      <c r="P100">
+        <v>-17.26377349547916</v>
+      </c>
+      <c r="Q100">
+        <v>-15.03377349547916</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.317315568794704</v>
+      </c>
+      <c r="T100">
+        <v>47.25628514827254</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.04053164020479718</v>
+      </c>
+      <c r="W100">
+        <v>0.2291210443190944</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.1621265608191887</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2928849348086067</v>
+      </c>
+      <c r="C101">
+        <v>-85.40121115149313</v>
+      </c>
+      <c r="D101">
+        <v>29.49610422655567</v>
+      </c>
+      <c r="E101">
+        <v>22.82608772345405</v>
+      </c>
+      <c r="F101">
+        <v>116.2173153780488</v>
+      </c>
+      <c r="G101">
+        <v>1.32</v>
+      </c>
+      <c r="H101">
+        <v>24</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>6.684</v>
+      </c>
+      <c r="K101">
+        <v>2.23</v>
+      </c>
+      <c r="L101">
+        <v>4.454000000000001</v>
+      </c>
+      <c r="M101">
+        <v>27.75269491227805</v>
+      </c>
+      <c r="N101">
+        <v>-23.29869491227805</v>
+      </c>
+      <c r="O101">
+        <v>-5.824673728069513</v>
+      </c>
+      <c r="P101">
+        <v>-17.47402118420854</v>
+      </c>
+      <c r="Q101">
+        <v>-15.24402118420854</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>6.595831137589408</v>
+      </c>
+      <c r="T101">
+        <v>94.51257029654508</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.04012222969767802</v>
+      </c>
+      <c r="W101">
+        <v>0.2292188115481945</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.160488918790712</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
